--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I209"/>
+  <dimension ref="A1:I230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5225,210 +5225,210 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>114/12/01</t>
+          <t>114/11/03</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>103003085</t>
+          <t>140157410</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>6,350,023,506</t>
+          <t>9,004,715,647</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>64.45</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>64.80</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.40</t>
+          <t>63.90</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>61.50</t>
+          <t>64.15</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>105,261</t>
+          <t>154,188</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>114/12/02</t>
+          <t>114/11/04</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>43152711</t>
+          <t>88131032</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2,670,762,886</t>
+          <t>5,658,007,897</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>64.50</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>62.20</t>
+          <t>64.85</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.65</t>
+          <t>63.85</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>61.70</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>+0.20</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>33,675</t>
+          <t>90,876</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>114/12/03</t>
+          <t>114/11/05</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>46546830</t>
+          <t>229413552</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2,900,511,764</t>
+          <t>14,391,151,897</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>62.30</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>62.30</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>+0.60</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>34,300</t>
+          <t>276,109</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>114/12/04</t>
+          <t>114/11/06</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>40655322</t>
+          <t>68680372</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2,530,843,780</t>
+          <t>4,349,732,858</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>63.50</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>62.00</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>62.20</t>
+          <t>63.30</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>35,535</t>
+          <t>57,358</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>114/12/05</t>
+          <t>114/11/07</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>47277037</t>
+          <t>111187957</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2,958,378,181</t>
+          <t>6,952,850,646</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>62.45</t>
+          <t>62.65</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5438,430 +5438,430 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>62.55</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>+0.55</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>44,751</t>
+          <t>136,880</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>114/12/08</t>
+          <t>114/11/10</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>78686347</t>
+          <t>83130868</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4,991,038,407</t>
+          <t>5,234,605,606</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>62.80</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>62.60</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>+0.95</t>
+          <t>+0.80</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>60,124</t>
+          <t>61,928</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>114/12/09</t>
+          <t>114/11/11</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>50671148</t>
+          <t>79723934</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>3,225,750,796</t>
+          <t>5,046,877,473</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>63.80</t>
+          <t>63.65</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>63.85</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>63.55</t>
+          <t>62.85</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>63.60</t>
+          <t>62.90</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>49,273</t>
+          <t>85,077</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>114/12/10</t>
+          <t>114/11/12</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>66717948</t>
+          <t>62620173</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>4,264,783,464</t>
+          <t>3,947,348,693</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>63.30</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>63.65</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>64.05</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>+0.30</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>51,254</t>
+          <t>55,267</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>114/12/11</t>
+          <t>114/11/13</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>101197570</t>
+          <t>80483242</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>6,442,627,838</t>
+          <t>5,053,859,324</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>64.30</t>
+          <t>62.80</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>64.50</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>62.60</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>63.35</t>
+          <t>62.90</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>110,925</t>
+          <t>89,344</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>114/12/12</t>
+          <t>114/11/14</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>60240146</t>
+          <t>223192943</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>3,825,611,936</t>
+          <t>13,766,027,280</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>63.55</t>
+          <t>61.65</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>63.80</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>63.30</t>
+          <t>61.40</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>63.45</t>
+          <t>61.70</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>+0.10</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>49,189</t>
+          <t>277,389</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>114/12/15</t>
+          <t>114/11/17</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>114939409</t>
+          <t>91925734</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>7,203,513,013</t>
+          <t>5,696,893,851</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>62.00</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>62.85</t>
+          <t>62.20</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>62.80</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>+0.20</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>134,546</t>
+          <t>85,395</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>114/12/16</t>
+          <t>114/11/18</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>169375708</t>
+          <t>264956405</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>10,494,294,870</t>
+          <t>16,077,471,840</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>61.30</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>62.25</t>
+          <t>61.30</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.70</t>
+          <t>60.30</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>62.25</t>
+          <t>60.45</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>211,332</t>
+          <t>354,183</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>114/12/17</t>
+          <t>114/11/19</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>98504980</t>
+          <t>151383859</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>6,122,747,371</t>
+          <t>9,097,742,490</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>62.15</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>62.45</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.85</t>
+          <t>59.90</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>61.90</t>
+          <t>60.05</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>86,356</t>
+          <t>198,226</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>114/12/18</t>
+          <t>114/11/20</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>117973409</t>
+          <t>84027889</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>7,287,940,742</t>
+          <t>5,187,294,354</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>61.55</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.55</t>
+          <t>61.35</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5871,237 +5871,237 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+1.85</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>87,078</t>
+          <t>61,552</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>114/12/19</t>
+          <t>114/11/21</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>81027467</t>
+          <t>327691489</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>5,067,295,440</t>
+          <t>19,593,794,724</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>59.50</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>59.85</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>+0.60</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>41,675</t>
+          <t>410,104</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>114/12/22</t>
+          <t>114/11/24</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>93882538</t>
+          <t>162722018</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>5,942,586,403</t>
+          <t>9,712,201,417</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>63.30</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>63.45</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>63.05</t>
+          <t>59.45</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>63.40</t>
+          <t>59.55</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>+0.90</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>52,777</t>
+          <t>155,513</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>114/12/23</t>
+          <t>114/11/25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>101867829</t>
+          <t>64411018</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>6,483,053,926</t>
+          <t>3,893,075,835</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>63.50</t>
+          <t>60.70</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>63.80</t>
+          <t>60.75</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>63.50</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>60.35</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>+0.30</t>
+          <t>+0.80</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>44,429</t>
+          <t>51,135</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>114/12/24</t>
+          <t>114/11/26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>64106420</t>
+          <t>75793554</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>4,094,914,827</t>
+          <t>4,646,516,112</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>61.10</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>64.05</t>
+          <t>61.50</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>63.75</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>63.85</t>
+          <t>61.35</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>+1.00</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>41,909</t>
+          <t>49,069</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>114/12/26</t>
+          <t>114/11/27</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>70816194</t>
+          <t>53852335</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>4,556,213,637</t>
+          <t>3,333,400,290</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>64.50</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>64.10</t>
+          <t>61.65</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>64.40</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6111,4143 +6111,5130 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>54,305</t>
+          <t>39,232</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>114/12/29</t>
+          <t>114/11/28</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>86510015</t>
+          <t>68386478</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>5,628,464,300</t>
+          <t>4,252,497,861</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>64.65</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>65.35</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>64.60</t>
+          <t>61.85</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>65.25</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>+0.85</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>63,528</t>
+          <t>37,281</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>114/12/30</t>
+          <t>114/12/01</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>61058197</t>
+          <t>103003085</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>3,970,585,296</t>
+          <t>6,350,023,506</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>64.90</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>65.30</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>64.75</t>
+          <t>61.40</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>61.50</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>54,458</t>
+          <t>105,261</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>114/12/31</t>
+          <t>114/12/02</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>71868485</t>
+          <t>43152711</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>4,709,518,474</t>
+          <t>2,670,762,886</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>65.10</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>62.20</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>64.90</t>
+          <t>61.65</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>65.60</t>
+          <t>61.70</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>+0.20</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>52,512</t>
+          <t>33,675</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>115/01/02</t>
+          <t>114/12/03</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>81135717</t>
+          <t>46546830</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>5,396,295,605</t>
+          <t>2,900,511,764</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>66.00</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>67.00</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>65.80</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>62.30</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>+1.35</t>
+          <t>+0.60</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>69,896</t>
+          <t>34,300</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>115/01/05</t>
+          <t>114/12/04</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>232910010</t>
+          <t>40655322</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>16,163,783,922</t>
+          <t>2,530,843,780</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>68.10</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>68.05</t>
+          <t>62.00</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>69.50</t>
+          <t>62.20</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>+2.55</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>141,745</t>
+          <t>35,535</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>115/01/06</t>
+          <t>114/12/05</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>130176548</t>
+          <t>47277037</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>9,090,693,014</t>
+          <t>2,958,378,181</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>69.45</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>70.40</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>68.95</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>70.40</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>+0.90</t>
+          <t>+0.55</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>94,772</t>
+          <t>44,751</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>115/01/07</t>
+          <t>114/12/08</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>122267721</t>
+          <t>78686347</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>8,554,349,889</t>
+          <t>4,991,038,407</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>70.40</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.70</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>+0.95</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>132,657</t>
+          <t>60,124</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>115/01/08</t>
+          <t>114/12/09</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>74866080</t>
+          <t>50671148</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>5,233,314,685</t>
+          <t>3,225,750,796</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>69.65</t>
+          <t>63.80</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>63.85</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.40</t>
+          <t>63.55</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>70.10</t>
+          <t>63.60</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>65,275</t>
+          <t>49,273</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>115/01/09</t>
+          <t>114/12/10</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>113278257</t>
+          <t>66717948</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>7,882,596,065</t>
+          <t>4,264,783,464</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>69.80</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>68.90</t>
+          <t>63.65</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>64.05</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>117,481</t>
+          <t>51,254</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>115/01/12</t>
+          <t>114/12/11</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>84346348</t>
+          <t>101197570</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>5,928,941,344</t>
+          <t>6,442,627,838</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>70.50</t>
+          <t>64.30</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>70.55</t>
+          <t>64.50</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>+0.50</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>74,258</t>
+          <t>110,925</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>115/01/13</t>
+          <t>114/12/12</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>103565147</t>
+          <t>60240146</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>7,323,170,787</t>
+          <t>3,825,611,936</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>71.10</t>
+          <t>63.55</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>71.20</t>
+          <t>63.80</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>70.30</t>
+          <t>63.30</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>70.70</t>
+          <t>63.45</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>+0.35</t>
+          <t>+0.10</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>77,504</t>
+          <t>49,189</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>115/01/14</t>
+          <t>114/12/15</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>86322515</t>
+          <t>114939409</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>6,115,431,229</t>
+          <t>7,203,513,013</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>70.95</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>71.10</t>
+          <t>62.85</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>70.65</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>70.75</t>
+          <t>62.80</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>+0.05</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>67,445</t>
+          <t>134,546</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>115/01/15</t>
+          <t>114/12/16</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>97455363</t>
+          <t>169375708</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>6,856,607,422</t>
+          <t>10,494,294,870</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>70.70</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>70.70</t>
+          <t>62.25</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>61.70</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>70.65</t>
+          <t>62.25</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>122,171</t>
+          <t>211,332</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>115/01/16</t>
+          <t>114/12/17</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>101069992</t>
+          <t>98504980</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>7,242,693,243</t>
+          <t>6,122,747,371</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>62.15</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>72.10</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>71.20</t>
+          <t>61.85</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>+1.35</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>80,151</t>
+          <t>86,356</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>115/01/19</t>
+          <t>114/12/18</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>122970595</t>
+          <t>117973409</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>8,839,245,132</t>
+          <t>7,287,940,742</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>72.80</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>61.55</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>72.60</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>+0.60</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>107,729</t>
+          <t>87,078</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>115/01/20</t>
+          <t>114/12/19</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>111046335</t>
+          <t>81027467</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>8,024,448,821</t>
+          <t>5,067,295,440</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>71.90</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>72.65</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>72.60</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+0.60</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>99,563</t>
+          <t>41,675</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>115/01/21</t>
+          <t>114/12/22</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>173683092</t>
+          <t>93882538</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>12,502,883,011</t>
+          <t>5,942,586,403</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>71.80</t>
+          <t>63.30</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>72.50</t>
+          <t>63.45</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>63.40</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.90</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>203,410</t>
+          <t>52,777</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>115/01/22</t>
+          <t>114/12/23</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>101703005</t>
+          <t>101867829</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>7,306,066,892</t>
+          <t>6,483,053,926</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>71.90</t>
+          <t>63.50</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>72.05</t>
+          <t>63.80</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>71.60</t>
+          <t>63.50</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>71.80</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>X0.00</t>
+          <t>+0.30</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>92,128</t>
+          <t>44,429</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>115/01/23</t>
+          <t>114/12/24</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>70983017</t>
+          <t>64106420</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>5,116,365,718</t>
+          <t>4,094,914,827</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>72.10</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>72.30</t>
+          <t>64.05</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>71.80</t>
+          <t>63.75</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>63.85</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>49,675</t>
+          <t>41,909</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>115/01/26</t>
+          <t>114/12/26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>87992466</t>
+          <t>70816194</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>6,373,835,828</t>
+          <t>4,556,213,637</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>72.65</t>
+          <t>64.50</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>64.10</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>64.40</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+0.55</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>72,487</t>
+          <t>54,305</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>115/01/27</t>
+          <t>114/12/29</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>73059634</t>
+          <t>86510015</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>5,322,600,617</t>
+          <t>5,628,464,300</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>72.40</t>
+          <t>64.65</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>65.35</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>64.60</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>65.25</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>+0.80</t>
+          <t>+0.85</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>53,680</t>
+          <t>63,528</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>115/01/28</t>
+          <t>114/12/30</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>90901846</t>
+          <t>61058197</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>6,711,076,738</t>
+          <t>3,970,585,296</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>73.55</t>
+          <t>64.90</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>74.20</t>
+          <t>65.30</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>73.50</t>
+          <t>64.75</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>74.20</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>+1.15</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>67,825</t>
+          <t>54,458</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>115/01/29</t>
+          <t>114/12/31</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>119914950</t>
+          <t>71868485</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>8,867,286,368</t>
+          <t>4,709,518,474</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>74.40</t>
+          <t>65.10</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>74.50</t>
+          <t>65.85</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>73.50</t>
+          <t>64.90</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>65.60</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>121,772</t>
+          <t>52,512</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>115/01/30</t>
+          <t>115/01/02</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>175275799</t>
+          <t>81135717</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>12,738,811,404</t>
+          <t>5,396,295,605</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>66.00</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>73.20</t>
+          <t>67.00</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>72.30</t>
+          <t>65.80</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>72.60</t>
+          <t>66.95</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>+1.35</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>241,546</t>
+          <t>69,896</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>115/02/02</t>
+          <t>115/01/05</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>234325396</t>
+          <t>232910010</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>16,687,566,456</t>
+          <t>16,163,783,922</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>71.55</t>
+          <t>68.10</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>70.90</t>
+          <t>68.05</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>71.50</t>
+          <t>69.50</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>+2.55</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>332,048</t>
+          <t>141,745</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>115/02/03</t>
+          <t>115/01/06</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>73734001</t>
+          <t>130176548</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>5,367,935,502</t>
+          <t>9,090,693,014</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>73.00</t>
+          <t>69.45</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>70.40</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>72.40</t>
+          <t>68.95</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>72.95</t>
+          <t>70.40</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>+1.45</t>
+          <t>+0.90</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>60,314</t>
+          <t>94,772</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>115/02/04</t>
+          <t>115/01/07</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>59733704</t>
+          <t>122267721</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>4,346,370,749</t>
+          <t>8,554,349,889</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>72.40</t>
+          <t>70.40</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>72.30</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>72.90</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>55,518</t>
+          <t>132,657</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>115/02/05</t>
+          <t>115/01/08</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>107575796</t>
+          <t>74866080</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>7,742,810,789</t>
+          <t>5,233,314,685</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>72.05</t>
+          <t>69.65</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>70.35</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>69.40</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>70.10</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>175,926</t>
+          <t>65,275</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>115/02/06</t>
+          <t>115/01/09</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>110883112</t>
+          <t>113278257</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>7,920,520,483</t>
+          <t>7,882,596,065</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>71.40</t>
+          <t>69.80</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>70.80</t>
+          <t>68.90</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>71.90</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>134,413</t>
+          <t>117,481</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>115/02/09</t>
+          <t>115/01/12</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>122340661</t>
+          <t>84346348</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>9,050,873,718</t>
+          <t>5,928,941,344</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>74.05</t>
+          <t>70.50</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>74.15</t>
+          <t>70.55</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>70.35</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>+2.05</t>
+          <t>+0.50</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>81,342</t>
+          <t>74,258</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>115/02/10</t>
+          <t>115/01/13</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>102315945</t>
+          <t>103565147</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>7,703,131,124</t>
+          <t>7,323,170,787</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>74.65</t>
+          <t>71.10</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>71.20</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>74.60</t>
+          <t>70.30</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>70.70</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>+1.55</t>
+          <t>+0.35</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>80,773</t>
+          <t>77,504</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>115/02/11</t>
+          <t>115/01/14</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>120639150</t>
+          <t>86322515</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>9,275,271,308</t>
+          <t>6,115,431,229</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>70.95</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>77.45</t>
+          <t>71.10</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>70.65</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>77.20</t>
+          <t>70.75</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>+1.70</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>118,568</t>
+          <t>67,445</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>115/02/23</t>
+          <t>115/01/15</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>227936939</t>
+          <t>97455363</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>17,749,552,954</t>
+          <t>6,856,607,422</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>70.70</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>70.70</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>77.20</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>77.40</t>
+          <t>70.65</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>+0.20</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>220,396</t>
+          <t>122,171</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>115/02/24</t>
+          <t>115/01/16</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>150367766</t>
+          <t>101069992</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>11,848,589,798</t>
+          <t>7,242,693,243</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>77.95</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>79.65</t>
+          <t>72.10</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>77.85</t>
+          <t>71.20</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>79.40</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>+2.00</t>
+          <t>+1.35</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>117,830</t>
+          <t>80,151</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>115/02/25</t>
+          <t>115/01/19</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>167423484</t>
+          <t>122970595</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>13,565,896,459</t>
+          <t>8,839,245,132</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>81.80</t>
+          <t>72.80</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>71.45</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>81.10</t>
+          <t>72.60</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>+1.70</t>
+          <t>+0.60</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>141,615</t>
+          <t>107,729</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>115/02/26</t>
+          <t>115/01/20</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>133517321</t>
+          <t>111046335</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>10,841,079,880</t>
+          <t>8,024,448,821</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>71.90</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>81.50</t>
+          <t>72.65</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>80.80</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>81.15</t>
+          <t>72.60</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>+0.05</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>133,768</t>
+          <t>99,563</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>115/03/02</t>
+          <t>115/01/21</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>224651381</t>
+          <t>173683092</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>18,053,460,439</t>
+          <t>12,502,883,011</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>79.50</t>
+          <t>71.80</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>80.80</t>
+          <t>72.50</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>79.15</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>297,372</t>
+          <t>203,410</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>115/03/03</t>
+          <t>115/01/22</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>324317518</t>
+          <t>101703005</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>25,713,110,082</t>
+          <t>7,306,066,892</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>80.05</t>
+          <t>71.90</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>80.40</t>
+          <t>72.05</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>78.65</t>
+          <t>71.60</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>71.80</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>X0.00</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>516,152</t>
+          <t>92,128</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>115/03/04</t>
+          <t>115/01/23</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>505217770</t>
+          <t>70983017</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>38,471,650,068</t>
+          <t>5,116,365,718</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>77.40</t>
+          <t>72.10</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>77.45</t>
+          <t>72.30</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>71.80</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>711,329</t>
+          <t>49,675</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>115/03/05</t>
+          <t>115/01/26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>207004644</t>
+          <t>87992466</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>16,090,040,992</t>
+          <t>6,373,835,828</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>78.30</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>78.85</t>
+          <t>72.65</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>76.70</t>
+          <t>72.20</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>77.40</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>+1.80</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>204,272</t>
+          <t>72,487</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>115/03/06</t>
+          <t>115/01/27</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>151611764</t>
+          <t>73059634</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>11,638,160,681</t>
+          <t>5,322,600,617</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>76.80</t>
+          <t>72.40</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>77.30</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>72.35</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>76.85</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>+0.80</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>179,651</t>
+          <t>53,680</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>115/03/09</t>
+          <t>115/01/28</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>542230074</t>
+          <t>90901846</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>39,488,306,757</t>
+          <t>6,711,076,738</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>73.55</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>73.60</t>
+          <t>74.20</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>71.65</t>
+          <t>73.50</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>73.60</t>
+          <t>74.20</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>+1.15</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>658,991</t>
+          <t>67,825</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>115/03/10</t>
+          <t>115/01/29</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>173870150</t>
+          <t>119914950</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>13,134,447,601</t>
+          <t>8,867,286,368</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>74.40</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>74.50</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>74.30</t>
+          <t>73.50</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>75.20</t>
+          <t>73.75</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>+1.60</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>180,826</t>
+          <t>121,772</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>115/03/11</t>
+          <t>115/01/30</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>151798656</t>
+          <t>175275799</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>11,785,499,671</t>
+          <t>12,738,811,404</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>78.50</t>
+          <t>73.20</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>72.30</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>78.20</t>
+          <t>72.60</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>+3.00</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>104,693</t>
+          <t>241,546</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>115/03/12</t>
+          <t>115/02/02</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>131518817</t>
+          <t>234325396</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>10,107,953,882</t>
+          <t>16,687,566,456</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>77.10</t>
+          <t>71.55</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>77.60</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>76.35</t>
+          <t>70.90</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>76.60</t>
+          <t>71.50</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>180,533</t>
+          <t>332,048</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>115/03/13</t>
+          <t>115/02/03</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>115111624</t>
+          <t>73734001</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>8,723,084,020</t>
+          <t>5,367,935,502</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>75.15</t>
+          <t>73.00</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>76.55</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>72.40</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>75.95</t>
+          <t>72.95</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>+1.45</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>160,164</t>
+          <t>60,314</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>115/03/16</t>
+          <t>115/02/04</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>105392137</t>
+          <t>59733704</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>7,994,232,270</t>
+          <t>4,346,370,749</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>72.40</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>76.70</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>75.45</t>
+          <t>72.30</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>72.90</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>135,317</t>
+          <t>55,518</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>115/03/17</t>
+          <t>115/02/05</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>63986997</t>
+          <t>107575796</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>4,901,077,314</t>
+          <t>7,742,810,789</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>72.05</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>77.00</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>76.65</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>+1.05</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>54,634</t>
+          <t>175,926</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>115/03/18</t>
+          <t>115/02/06</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>78000193</t>
+          <t>110883112</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>6,064,253,100</t>
+          <t>7,920,520,483</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>77.75</t>
+          <t>71.40</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>78.05</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>77.45</t>
+          <t>70.80</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>77.80</t>
+          <t>71.90</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>+1.15</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>65,062</t>
+          <t>134,413</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>115/03/19</t>
+          <t>115/02/09</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>141733755</t>
+          <t>122340661</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>10,821,638,440</t>
+          <t>9,050,873,718</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>76.60</t>
+          <t>74.05</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>76.80</t>
+          <t>74.15</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>75.95</t>
+          <t>73.75</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>76.00</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>+2.05</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>218,952</t>
+          <t>81,342</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>115/03/20</t>
+          <t>115/02/10</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>72638922</t>
+          <t>102315945</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>5,517,624,557</t>
+          <t>7,703,131,124</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>76.20</t>
+          <t>74.65</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>76.40</t>
+          <t>75.50</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
+          <t>74.60</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
           <t>75.50</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>75.90</t>
-        </is>
-      </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+1.55</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>101,109</t>
+          <t>80,773</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>115/03/23</t>
+          <t>115/02/11</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>233385121</t>
+          <t>120639150</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>17,256,278,289</t>
+          <t>9,275,271,308</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>73.50</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>74.45</t>
+          <t>77.45</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>73.30</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>77.20</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>+1.70</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>340,169</t>
+          <t>118,568</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>115/03/24</t>
+          <t>115/02/23</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>90466270</t>
+          <t>227936939</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>6,750,345,110</t>
+          <t>17,749,552,954</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>73.80</t>
+          <t>77.20</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>74.40</t>
+          <t>77.40</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>+0.20</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>111,636</t>
+          <t>220,396</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>115/03/25</t>
+          <t>115/02/24</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>94344080</t>
+          <t>150367766</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>7,201,277,589</t>
+          <t>11,848,589,798</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>76.35</t>
+          <t>77.95</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>76.65</t>
+          <t>79.65</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>76.00</t>
+          <t>77.85</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>76.20</t>
+          <t>79.40</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>+1.80</t>
+          <t>+2.00</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>66,655</t>
+          <t>117,830</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>115/03/26</t>
+          <t>115/02/25</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>80069071</t>
+          <t>167423484</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>6,102,674,371</t>
+          <t>13,565,896,459</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>76.85</t>
+          <t>81.80</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>75.80</t>
+          <t>81.10</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>+1.70</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>80,270</t>
+          <t>141,615</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>115/03/27</t>
+          <t>115/02/26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>115798710</t>
+          <t>133517321</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>8,622,872,378</t>
+          <t>10,841,079,880</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>74.45</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>75.10</t>
+          <t>81.50</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>74.10</t>
+          <t>80.80</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>81.15</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>161,501</t>
+          <t>133,768</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>115/03/30</t>
+          <t>115/03/02</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>175515568</t>
+          <t>224651381</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>12,905,676,995</t>
+          <t>18,053,460,439</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>73.30</t>
+          <t>79.50</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>74.05</t>
+          <t>80.80</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>72.80</t>
+          <t>79.15</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>261,697</t>
+          <t>297,372</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>115/03/31</t>
+          <t>115/03/03</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>257738774</t>
+          <t>324317518</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>18,741,416,482</t>
+          <t>25,713,110,082</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>73.35</t>
+          <t>80.05</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>73.45</t>
+          <t>80.40</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>72.15</t>
+          <t>78.65</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>78.75</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>400,630</t>
+          <t>516,152</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>115/04/01</t>
+          <t>115/03/04</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>130698663</t>
+          <t>505217770</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>9,824,716,760</t>
+          <t>38,471,650,068</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>77.40</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
+          <t>77.45</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>75.50</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
           <t>75.60</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>74.60</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>75.45</t>
-        </is>
-      </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>+3.10</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>89,221</t>
+          <t>711,329</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>115/04/02</t>
+          <t>115/03/05</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>113976137</t>
+          <t>207004644</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>8,478,357,215</t>
+          <t>16,090,040,992</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>78.85</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>73.80</t>
+          <t>76.70</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>77.40</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>+1.80</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>162,558</t>
+          <t>204,272</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>115/04/07</t>
+          <t>115/03/06</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>80449813</t>
+          <t>151611764</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>6,046,717,969</t>
+          <t>11,638,160,681</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>75.15</t>
+          <t>76.80</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>75.45</t>
+          <t>77.30</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>74.65</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>75.30</t>
+          <t>76.85</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>+1.35</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>81,117</t>
+          <t>179,651</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>115/04/08</t>
+          <t>115/03/09</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>235675856</t>
+          <t>542230074</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>18,578,257,980</t>
+          <t>39,488,306,757</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>78.10</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>79.25</t>
+          <t>73.60</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>78.10</t>
+          <t>71.65</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>79.20</t>
+          <t>73.60</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>+3.90</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>148,473</t>
+          <t>658,991</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>115/04/09</t>
+          <t>115/03/10</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>95094893</t>
+          <t>173870150</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>7,520,522,079</t>
+          <t>13,134,447,601</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>79.30</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>79.40</t>
+          <t>76.25</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>78.80</t>
+          <t>74.30</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>79.15</t>
+          <t>75.20</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>+1.60</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>72,839</t>
+          <t>180,826</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>115/04/10</t>
+          <t>115/03/11</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>120838644</t>
+          <t>151798656</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>9,724,171,699</t>
+          <t>11,785,499,671</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>80.80</t>
+          <t>78.50</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>79.95</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>78.20</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>+1.60</t>
+          <t>+3.00</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>98,770</t>
+          <t>104,693</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>115/04/13</t>
+          <t>115/03/12</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>91689847</t>
+          <t>131518817</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>7,398,471,916</t>
+          <t>10,107,953,882</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>80.60</t>
+          <t>77.10</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>81.00</t>
+          <t>77.60</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>80.40</t>
+          <t>76.35</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>80.60</t>
+          <t>76.60</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>86,103</t>
+          <t>180,533</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>115/04/14</t>
+          <t>115/03/13</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>129128623</t>
+          <t>115111624</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>10,668,730,259</t>
+          <t>8,723,084,020</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>81.75</t>
+          <t>75.15</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>83.20</t>
+          <t>76.55</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>81.75</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>83.10</t>
+          <t>75.95</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>+2.50</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>101,069</t>
+          <t>160,164</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>115/04/15</t>
+          <t>115/03/16</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>127729350</t>
+          <t>105392137</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>10,793,181,456</t>
+          <t>7,994,232,270</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>84.10</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>85.10</t>
+          <t>76.70</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>83.80</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>+1.05</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>122,459</t>
+          <t>135,317</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>115/04/16</t>
+          <t>115/03/17</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>80696269</t>
+          <t>63986997</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>6,829,488,057</t>
+          <t>4,901,077,314</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>85.10</t>
+          <t>77.00</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>76.65</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>+0.85</t>
+          <t>+1.05</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>78,794</t>
+          <t>54,634</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>115/04/17</t>
+          <t>115/03/18</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>101258031</t>
+          <t>78000193</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>8,526,065,307</t>
+          <t>6,064,253,100</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>84.20</t>
+          <t>77.75</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>84.50</t>
+          <t>78.05</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>84.00</t>
+          <t>77.45</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>77.80</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>+1.15</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>146,785</t>
+          <t>65,062</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>115/04/20</t>
+          <t>115/03/19</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>100551500</t>
+          <t>141733755</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>8,533,691,370</t>
+          <t>10,821,638,440</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>84.55</t>
+          <t>76.60</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>85.10</t>
+          <t>76.80</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>84.45</t>
+          <t>75.95</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>84.55</t>
+          <t>76.00</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>+0.40</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>90,566</t>
+          <t>218,952</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>115/04/21</t>
+          <t>115/03/20</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>75557759</t>
+          <t>72638922</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>6,477,242,890</t>
+          <t>5,517,624,557</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>85.50</t>
+          <t>76.20</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>86.10</t>
+          <t>76.40</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>75.50</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>86.00</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>+1.45</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>72,495</t>
+          <t>101,109</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>115/04/22</t>
+          <t>115/03/23</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>67544248</t>
+          <t>233385121</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>5,828,004,375</t>
+          <t>17,256,278,289</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>85.75</t>
+          <t>73.50</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>74.45</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>85.55</t>
+          <t>73.30</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>86.35</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>+0.35</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>70,385</t>
+          <t>340,169</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>115/04/23</t>
+          <t>115/03/24</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>156715780</t>
+          <t>90466270</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>13,599,617,688</t>
+          <t>6,750,345,110</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>87.65</t>
+          <t>75.50</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>88.80</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>73.80</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>86.35</t>
+          <t>74.40</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>161,030</t>
+          <t>111,636</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>115/04/24</t>
+          <t>115/03/25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>129885911</t>
+          <t>94344080</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>11,539,759,376</t>
+          <t>7,201,277,589</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>87.60</t>
+          <t>76.35</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>76.65</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>87.55</t>
+          <t>76.00</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>76.20</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>+3.60</t>
+          <t>+1.80</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>99,531</t>
+          <t>66,655</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>115/04/27</t>
+          <t>115/03/26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>192038103</t>
+          <t>80069071</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>17,927,615,310</t>
+          <t>6,102,674,371</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>92.70</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>76.85</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>92.70</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>93.00</t>
+          <t>75.80</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>+3.05</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>172,215</t>
+          <t>80,270</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>115/04/28</t>
+          <t>115/03/27</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>126301332</t>
+          <t>115798710</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>11,691,553,456</t>
+          <t>8,622,872,378</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>92.55</t>
+          <t>74.45</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>93.65</t>
+          <t>75.10</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>91.90</t>
+          <t>74.10</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>92.00</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>193,633</t>
+          <t>161,501</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>115/04/29</t>
+          <t>115/03/30</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>103795530</t>
+          <t>175515568</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>9,410,136,420</t>
+          <t>12,905,676,995</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>90.70</t>
+          <t>73.30</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>91.50</t>
+          <t>74.05</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>90.00</t>
+          <t>72.80</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>90.75</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>163,856</t>
+          <t>261,697</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>115/04/30</t>
+          <t>115/03/31</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>89209769</t>
+          <t>257738774</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>8,111,730,781</t>
+          <t>18,741,416,482</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>91.25</t>
+          <t>73.35</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>91.90</t>
+          <t>73.45</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>90.30</t>
+          <t>72.15</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>90.50</t>
+          <t>72.35</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>125,264</t>
+          <t>400,630</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>115/05/04</t>
+          <t>115/04/01</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>125270935</t>
+          <t>130698663</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>11,748,311,547</t>
+          <t>9,824,716,760</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>92.50</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>94.65</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>92.40</t>
+          <t>74.60</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>94.60</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>+4.10</t>
+          <t>+3.10</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>114,510</t>
+          <t>89,221</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>115/05/05</t>
+          <t>115/04/02</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>82851869</t>
+          <t>113976137</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>7,821,971,023</t>
+          <t>8,478,357,215</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>94.40</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>94.75</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>94.00</t>
+          <t>73.80</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>94.60</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>115,951</t>
+          <t>162,558</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>115/05/06</t>
+          <t>115/04/07</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>111759164</t>
+          <t>80449813</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>10,703,702,958</t>
+          <t>6,046,717,969</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>96.05</t>
+          <t>75.15</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>96.90</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>94.70</t>
+          <t>74.65</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>95.75</t>
+          <t>75.30</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>+1.15</t>
+          <t>+1.35</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>120,555</t>
+          <t>81,117</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>115/05/07</t>
+          <t>115/04/08</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>117152238</t>
+          <t>235675856</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>11,472,448,704</t>
+          <t>18,578,257,980</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>97.95</t>
+          <t>78.10</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>98.40</t>
+          <t>79.25</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>97.40</t>
+          <t>78.10</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>97.70</t>
+          <t>79.20</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>+1.95</t>
+          <t>+3.90</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>119,685</t>
+          <t>148,473</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>115/05/08</t>
+          <t>115/04/09</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>131188123</t>
+          <t>95094893</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>12,716,275,565</t>
+          <t>7,520,522,079</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>97.35</t>
+          <t>79.30</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>97.70</t>
+          <t>79.40</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>95.85</t>
+          <t>78.80</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>97.00</t>
+          <t>79.15</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>217,822</t>
+          <t>72,839</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>115/05/11</t>
+          <t>115/04/10</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>96606391</t>
+          <t>120838644</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>9,362,479,353</t>
+          <t>9,724,171,699</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>96.65</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>97.15</t>
+          <t>80.80</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>96.50</t>
+          <t>79.95</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>96.90</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+1.60</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>148,902</t>
+          <t>98,770</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>115/05/12</t>
+          <t>115/04/13</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>102303450</t>
+          <t>91689847</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>9,876,959,425</t>
+          <t>7,398,471,916</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>96.85</t>
+          <t>80.60</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>97.35</t>
+          <t>81.00</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>95.50</t>
+          <t>80.40</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>96.85</t>
+          <t>80.60</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>142,949</t>
+          <t>86,103</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>115/05/13</t>
+          <t>115/04/14</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>130654061</t>
+          <t>129128623</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>12,419,149,243</t>
+          <t>10,668,730,259</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>94.85</t>
+          <t>81.75</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>95.80</t>
+          <t>83.20</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>94.70</t>
+          <t>81.75</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>95.50</t>
+          <t>83.10</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>+2.50</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>260,692</t>
+          <t>101,069</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>115/05/14</t>
+          <t>115/04/15</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>57229209</t>
+          <t>127729350</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>5,510,647,058</t>
+          <t>10,793,181,456</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>96.90</t>
+          <t>84.10</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>97.20</t>
+          <t>85.10</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>95.75</t>
+          <t>83.80</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>96.05</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>+0.55</t>
+          <t>+1.05</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>70,419</t>
+          <t>122,459</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
+          <t>115/04/16</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>80696269</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>6,829,488,057</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>84.75</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>85.10</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>84.15</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>85.00</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>+0.85</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>78,794</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>115/04/17</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>101258031</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>8,526,065,307</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>84.20</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>84.50</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>84.00</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>84.15</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>146,785</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>115/04/20</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>100551500</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>8,533,691,370</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>84.55</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>85.10</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>84.45</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>84.55</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>+0.40</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>90,566</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>115/04/21</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>75557759</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>6,477,242,890</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>85.50</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>86.10</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>85.00</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>86.00</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>+1.45</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>72,495</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>115/04/22</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>67544248</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>5,828,004,375</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>85.75</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>86.60</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>85.55</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>86.35</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>+0.35</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>70,385</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>115/04/23</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>156715780</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>13,599,617,688</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>87.65</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>88.80</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>85.15</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>86.35</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 0.00</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>161,030</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>115/04/24</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>129885911</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>11,539,759,376</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>87.60</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>87.55</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>89.95</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>+3.60</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>99,531</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>115/04/27</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>192038103</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>17,927,615,310</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>92.70</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>94.25</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>92.70</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>93.00</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>+3.05</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>172,215</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>115/04/28</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>126301332</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>11,691,553,456</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>92.55</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>93.65</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>91.90</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>92.00</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-1.00</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>193,633</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>115/04/29</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>103795530</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>9,410,136,420</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>90.70</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>91.50</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>90.75</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-1.25</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>163,856</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>115/04/30</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>89209769</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>8,111,730,781</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>91.25</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>91.90</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>90.30</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>90.50</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>125,264</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>115/05/04</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>125270935</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>11,748,311,547</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>92.50</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>94.65</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>92.40</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>94.60</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>+4.10</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>114,510</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>115/05/05</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>82851869</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>7,821,971,023</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>94.40</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>94.75</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>94.60</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 0.00</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>115,951</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>115/05/06</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>111759164</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>10,703,702,958</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>96.05</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>96.90</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>94.70</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>95.75</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>+1.15</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>120,555</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>115/05/07</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>117152238</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>11,472,448,704</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>97.95</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>98.40</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>97.40</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>97.70</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>+1.95</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>119,685</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>115/05/08</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>131188123</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>12,716,275,565</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>97.35</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>97.70</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>95.85</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>97.00</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-0.70</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>217,822</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>115/05/11</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>96606391</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>9,362,479,353</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>96.65</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>97.15</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>96.50</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>96.90</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>148,902</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>115/05/12</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>102303450</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>9,876,959,425</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>96.85</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>97.35</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>95.50</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>96.85</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>142,949</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>115/05/13</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>130654061</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>12,419,149,243</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>94.85</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>95.80</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>94.70</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>95.50</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>260,692</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>115/05/14</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>57229209</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>5,510,647,058</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>96.90</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>97.20</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>95.75</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>96.05</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>+0.55</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>70,419</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
           <t>115/05/15</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B229" t="inlineStr">
         <is>
           <t>98132989</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C229" t="inlineStr">
         <is>
           <t>9,472,541,597</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>97.65</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>98.25</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F229" t="inlineStr">
         <is>
           <t>95.20</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G229" t="inlineStr">
         <is>
           <t>95.40</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
+      <c r="H229" t="inlineStr">
         <is>
           <t>-0.65</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
+      <c r="I229" t="inlineStr">
         <is>
           <t>144,425</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>115/05/18</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>118571453</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>11,160,721,206</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>95.20</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>93.30</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>94.90</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>219,202</t>
         </is>
       </c>
     </row>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I230"/>
+  <dimension ref="A1:I231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11238,6 +11238,53 @@
         </is>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>115/05/19</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>135939820</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>12,740,872,880</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>94.35</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>94.70</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>93.10</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>93.10</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-1.80</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>304,750</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I231"/>
+  <dimension ref="A1:I232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11285,6 +11285,53 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>115/05/20</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>121650308</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>11,289,688,382</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>93.00</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>93.50</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>92.45</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>92.50</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>227,369</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I232"/>
+  <dimension ref="A1:I233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11332,6 +11332,53 @@
         </is>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>115/05/21</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>62215954</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>5,942,503,747</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>94.80</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>96.05</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>94.70</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>95.85</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>+3.35</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>64,187</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I233"/>
+  <dimension ref="A1:I234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11379,6 +11379,53 @@
         </is>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>115/05/22</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>64288280</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>6,213,742,970</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>96.30</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>97.30</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>96.00</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>97.30</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>+1.45</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>70,101</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I234"/>
+  <dimension ref="A1:I235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11426,6 +11426,53 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>115/05/25</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>129483256</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>13,010,032,076</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>99.55</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>99.55</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>100.80</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>+3.50</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>107,787</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I235"/>
+  <dimension ref="A1:I238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11473,6 +11473,147 @@
         </is>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>115/05/26</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>93560313</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>9,432,115,613</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>101.60</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>101.80</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>100.10</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>100.10</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-0.70</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>112,958</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>115/05/27</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>94959812</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>9,787,482,181</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>102.40</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>103.90</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>102.55</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>+2.45</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>98,413</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>115/05/28</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>152915695</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>15,600,509,184</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>104.00</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>104.25</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>100.10</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>100.50</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>207,536</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I238"/>
+  <dimension ref="A1:I239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11614,6 +11614,53 @@
         </is>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>115/05/29</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>102355526</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>10,636,250,508</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>103.20</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>105.40</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>102.70</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>105.40</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>+4.90</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>80,065</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I204"/>
+  <dimension ref="A1:I225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9032,987 +9032,1974 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>115/05/04</t>
+          <t>115/04/01</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>125270935</t>
+          <t>130698663</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>11,748,311,547</t>
+          <t>9,824,716,760</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>92.50</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>94.65</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>92.40</t>
+          <t>74.60</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>94.60</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>+4.10</t>
+          <t>+3.10</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>114,510</t>
+          <t>89,221</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>115/05/05</t>
+          <t>115/04/02</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>82851869</t>
+          <t>113976137</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>7,821,971,023</t>
+          <t>8,478,357,215</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>94.40</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>94.75</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>94.00</t>
+          <t>73.80</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>94.60</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>115,951</t>
+          <t>162,558</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>115/05/06</t>
+          <t>115/04/07</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>111759164</t>
+          <t>80449813</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>10,703,702,958</t>
+          <t>6,046,717,969</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>96.05</t>
+          <t>75.15</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>96.90</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>94.70</t>
+          <t>74.65</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>95.75</t>
+          <t>75.30</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>+1.15</t>
+          <t>+1.35</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>120,555</t>
+          <t>81,117</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>115/05/07</t>
+          <t>115/04/08</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>117152238</t>
+          <t>235675856</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>11,472,448,704</t>
+          <t>18,578,257,980</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>97.95</t>
+          <t>78.10</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>98.40</t>
+          <t>79.25</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>97.40</t>
+          <t>78.10</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>97.70</t>
+          <t>79.20</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>+1.95</t>
+          <t>+3.90</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>119,685</t>
+          <t>148,473</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>115/05/08</t>
+          <t>115/04/09</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>131188123</t>
+          <t>95094893</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>12,716,275,565</t>
+          <t>7,520,522,079</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>97.35</t>
+          <t>79.30</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>97.70</t>
+          <t>79.40</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>95.85</t>
+          <t>78.80</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>97.00</t>
+          <t>79.15</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>217,822</t>
+          <t>72,839</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>115/05/11</t>
+          <t>115/04/10</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>96606391</t>
+          <t>120838644</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>9,362,479,353</t>
+          <t>9,724,171,699</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>96.65</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>97.15</t>
+          <t>80.80</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>96.50</t>
+          <t>79.95</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>96.90</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+1.60</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>148,902</t>
+          <t>98,770</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>115/05/12</t>
+          <t>115/04/13</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>102303450</t>
+          <t>91689847</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>9,876,959,425</t>
+          <t>7,398,471,916</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>96.85</t>
+          <t>80.60</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>97.35</t>
+          <t>81.00</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>95.50</t>
+          <t>80.40</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>96.85</t>
+          <t>80.60</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>142,949</t>
+          <t>86,103</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>115/05/13</t>
+          <t>115/04/14</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>130654061</t>
+          <t>129128623</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>12,419,149,243</t>
+          <t>10,668,730,259</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>94.85</t>
+          <t>81.75</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>95.80</t>
+          <t>83.20</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>94.70</t>
+          <t>81.75</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>95.50</t>
+          <t>83.10</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>+2.50</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>260,692</t>
+          <t>101,069</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>115/05/14</t>
+          <t>115/04/15</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>57229209</t>
+          <t>127729350</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>5,510,647,058</t>
+          <t>10,793,181,456</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>96.90</t>
+          <t>84.10</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>97.20</t>
+          <t>85.10</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>95.75</t>
+          <t>83.80</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>96.05</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>+0.55</t>
+          <t>+1.05</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>70,419</t>
+          <t>122,459</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>115/05/15</t>
+          <t>115/04/16</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>98132989</t>
+          <t>80696269</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>9,472,541,597</t>
+          <t>6,829,488,057</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>97.65</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>98.25</t>
+          <t>85.10</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>95.20</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>95.40</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>+0.85</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>144,425</t>
+          <t>78,794</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>115/05/18</t>
+          <t>115/04/17</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>118571453</t>
+          <t>101258031</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>11,160,721,206</t>
+          <t>8,526,065,307</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>94.00</t>
+          <t>84.20</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>95.20</t>
+          <t>84.50</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>93.30</t>
+          <t>84.00</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>94.90</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>219,202</t>
+          <t>146,785</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>115/05/19</t>
+          <t>115/04/20</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>135939820</t>
+          <t>100551500</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>12,740,872,880</t>
+          <t>8,533,691,370</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>94.35</t>
+          <t>84.55</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>94.70</t>
+          <t>85.10</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>93.10</t>
+          <t>84.45</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>93.10</t>
+          <t>84.55</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>+0.40</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>304,750</t>
+          <t>90,566</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>115/05/20</t>
+          <t>115/04/21</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>121650308</t>
+          <t>75557759</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>11,289,688,382</t>
+          <t>6,477,242,890</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>93.00</t>
+          <t>85.50</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>93.50</t>
+          <t>86.10</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>92.45</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>92.50</t>
+          <t>86.00</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>+1.45</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>227,369</t>
+          <t>72,495</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>115/05/21</t>
+          <t>115/04/22</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>62215954</t>
+          <t>67544248</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>5,942,503,747</t>
+          <t>5,828,004,375</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>94.80</t>
+          <t>85.75</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>96.05</t>
+          <t>86.60</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>94.70</t>
+          <t>85.55</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>95.85</t>
+          <t>86.35</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>+3.35</t>
+          <t>+0.35</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>64,187</t>
+          <t>70,385</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>115/05/22</t>
+          <t>115/04/23</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>64288280</t>
+          <t>156715780</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>6,213,742,970</t>
+          <t>13,599,617,688</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>96.30</t>
+          <t>87.65</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>97.30</t>
+          <t>88.80</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>97.30</t>
+          <t>86.35</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>+1.45</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>70,101</t>
+          <t>161,030</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>115/05/25</t>
+          <t>115/04/24</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>129483256</t>
+          <t>129885911</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>13,010,032,076</t>
+          <t>11,539,759,376</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>99.55</t>
+          <t>87.60</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>101.00</t>
+          <t>89.95</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>99.55</t>
+          <t>87.55</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>100.80</t>
+          <t>89.95</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>+3.50</t>
+          <t>+3.60</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>107,787</t>
+          <t>99,531</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>115/05/26</t>
+          <t>115/04/27</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>93560313</t>
+          <t>192038103</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>9,432,115,613</t>
+          <t>17,927,615,310</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>101.60</t>
+          <t>92.70</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>101.80</t>
+          <t>94.25</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>100.10</t>
+          <t>92.70</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>100.10</t>
+          <t>93.00</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>+3.05</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>112,958</t>
+          <t>172,215</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>115/05/27</t>
+          <t>115/04/28</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>94959812</t>
+          <t>126301332</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>9,787,482,181</t>
+          <t>11,691,553,456</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>102.40</t>
+          <t>92.55</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>103.90</t>
+          <t>93.65</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>102.00</t>
+          <t>91.90</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>102.55</t>
+          <t>92.00</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>+2.45</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>98,413</t>
+          <t>193,633</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>115/05/28</t>
+          <t>115/04/29</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>152915695</t>
+          <t>103795530</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>15,600,509,184</t>
+          <t>9,410,136,420</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>104.00</t>
+          <t>90.70</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>104.25</t>
+          <t>91.50</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>100.10</t>
+          <t>90.00</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>100.50</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>207,536</t>
+          <t>163,856</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>115/05/29</t>
+          <t>115/04/30</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>102355526</t>
+          <t>89209769</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>10,636,250,508</t>
+          <t>8,111,730,781</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>103.20</t>
+          <t>91.25</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>105.40</t>
+          <t>91.90</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>102.70</t>
+          <t>90.30</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>105.40</t>
+          <t>90.50</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>+4.90</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>80,065</t>
+          <t>125,264</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
+          <t>115/05/04</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>125270935</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>11,748,311,547</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>92.50</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>94.65</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>92.40</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>94.60</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>+4.10</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>114,510</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>115/05/05</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>82851869</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>7,821,971,023</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>94.40</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>94.75</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>94.60</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 0.00</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>115,951</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>115/05/06</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>111759164</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>10,703,702,958</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>96.05</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>96.90</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>94.70</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>95.75</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>+1.15</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>120,555</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>115/05/07</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>117152238</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>11,472,448,704</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>97.95</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>98.40</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>97.40</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>97.70</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>+1.95</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>119,685</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>115/05/08</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>131188123</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>12,716,275,565</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>97.35</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>97.70</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>95.85</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>97.00</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-0.70</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>217,822</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>115/05/11</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>96606391</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>9,362,479,353</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>96.65</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>97.15</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>96.50</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>96.90</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>148,902</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>115/05/12</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>102303450</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>9,876,959,425</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>96.85</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>97.35</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>95.50</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>96.85</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>142,949</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>115/05/13</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>130654061</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>12,419,149,243</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>94.85</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>95.80</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>94.70</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>95.50</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>260,692</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>115/05/14</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>57229209</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>5,510,647,058</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>96.90</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>97.20</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>95.75</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>96.05</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>+0.55</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>70,419</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>115/05/15</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>98132989</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>9,472,541,597</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>97.65</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>98.25</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>95.20</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>95.40</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>144,425</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>115/05/18</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>118571453</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>11,160,721,206</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>95.20</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>93.30</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>94.90</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>219,202</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>115/05/19</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>135939820</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>12,740,872,880</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>94.35</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>94.70</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>93.10</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>93.10</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-1.80</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>304,750</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>115/05/20</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>121650308</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>11,289,688,382</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>93.00</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>93.50</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>92.45</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>92.50</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>227,369</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>115/05/21</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>62215954</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>5,942,503,747</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>94.80</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>96.05</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>94.70</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>95.85</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>+3.35</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>64,187</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>115/05/22</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>64288280</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>6,213,742,970</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>96.30</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>97.30</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>96.00</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>97.30</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>+1.45</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>70,101</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>115/05/25</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>129483256</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>13,010,032,076</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>99.55</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>99.55</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>100.80</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>+3.50</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>107,787</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>115/05/26</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>93560313</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>9,432,115,613</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>101.60</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>101.80</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>100.10</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>100.10</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-0.70</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>112,958</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>115/05/27</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>94959812</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>9,787,482,181</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>102.40</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>103.90</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>102.55</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>+2.45</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>98,413</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>115/05/28</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>152915695</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>15,600,509,184</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>104.00</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>104.25</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>100.10</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>100.50</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>207,536</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>115/05/29</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>102355526</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>10,636,250,508</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>103.20</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>105.40</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>102.70</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>105.40</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>+4.90</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>80,065</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
           <t>115/06/01</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>135817122</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="C224" t="inlineStr">
         <is>
           <t>14,329,024,058</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>105.25</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E224" t="inlineStr">
         <is>
           <t>106.70</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F224" t="inlineStr">
         <is>
           <t>104.50</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G224" t="inlineStr">
         <is>
           <t>105.50</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
+      <c r="H224" t="inlineStr">
         <is>
           <t>+0.10</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
+      <c r="I224" t="inlineStr">
         <is>
           <t>156,361</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>115/06/02</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>117160979</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>12,341,210,929</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>106.30</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>106.30</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>104.20</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>105.70</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>+0.20</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>164,814</t>
         </is>
       </c>
     </row>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I225"/>
+  <dimension ref="A1:I226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11003,6 +11003,53 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>115/06/03</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>79592362</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>8,559,208,311</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>107.30</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>107.85</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>107.10</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>107.60</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>+1.90</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>86,991</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I226"/>
+  <dimension ref="A1:I227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11050,6 +11050,53 @@
         </is>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>115/06/04</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>236782252</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>25,181,889,523</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>106.75</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>107.00</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>106.05</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>106.10</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-1.50</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>210,220</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I227"/>
+  <dimension ref="A1:I228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11097,6 +11097,53 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>115/06/05</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>337031371</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>34,914,259,576</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>105.00</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>105.35</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>102.80</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>104.15</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>355,384</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I228"/>
+  <dimension ref="A1:I208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,1150 +3533,1150 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>114/10/01</t>
+          <t>114/11/03</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>77291614</t>
+          <t>140157410</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>4,503,366,313</t>
+          <t>9,004,715,647</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>57.90</t>
+          <t>64.45</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>58.75</t>
+          <t>64.80</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>57.90</t>
+          <t>63.90</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>58.10</t>
+          <t>64.15</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>+0.30</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>59,386</t>
+          <t>154,188</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>114/10/02</t>
+          <t>114/11/04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>73803137</t>
+          <t>88131032</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>4,361,065,414</t>
+          <t>5,658,007,897</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>59.00</t>
+          <t>64.50</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>59.25</t>
+          <t>64.85</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>58.85</t>
+          <t>63.85</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>59.20</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>+1.10</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>45,593</t>
+          <t>90,876</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>114/10/03</t>
+          <t>114/11/05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>76083554</t>
+          <t>229413552</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>4,545,707,938</t>
+          <t>14,391,151,897</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>59.20</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>60.10</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>62.30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>60.05</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>+0.85</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>58,010</t>
+          <t>276,109</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>114/10/07</t>
+          <t>114/11/06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>138001575</t>
+          <t>68680372</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>8,474,594,769</t>
+          <t>4,349,732,858</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>61.00</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>61.70</t>
+          <t>63.50</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.90</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>61.70</t>
+          <t>63.30</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>+1.65</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>98,359</t>
+          <t>57,358</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>114/10/08</t>
+          <t>114/11/07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>119706336</t>
+          <t>111187957</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>7,282,646,193</t>
+          <t>6,952,850,646</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>61.00</t>
+          <t>62.65</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>61.15</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>60.60</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>61.15</t>
+          <t>62.55</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>117,731</t>
+          <t>136,880</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>114/10/09</t>
+          <t>114/11/10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>76478634</t>
+          <t>83130868</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>4,720,554,315</t>
+          <t>5,234,605,606</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>61.85</t>
+          <t>62.80</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.50</t>
+          <t>62.60</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>61.60</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>+0.80</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>62,822</t>
+          <t>61,928</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>114/10/13</t>
+          <t>114/11/11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>277610574</t>
+          <t>79723934</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>16,788,141,527</t>
+          <t>5,046,877,473</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>59.90</t>
+          <t>63.65</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>61.00</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>59.60</t>
+          <t>62.85</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>61.00</t>
+          <t>62.90</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>257,909</t>
+          <t>85,077</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>114/10/14</t>
+          <t>114/11/12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>163441296</t>
+          <t>62620173</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>10,048,295,024</t>
+          <t>3,947,348,693</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>61.85</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>62.15</t>
+          <t>63.30</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.65</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>60.70</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>+0.30</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>129,817</t>
+          <t>55,267</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>114/10/15</t>
+          <t>114/11/13</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>101918261</t>
+          <t>80483242</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>6,245,523,944</t>
+          <t>5,053,859,324</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>61.00</t>
+          <t>62.80</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>60.60</t>
+          <t>62.60</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>62.90</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>+1.10</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>69,593</t>
+          <t>89,344</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>114/10/16</t>
+          <t>114/11/14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>115801585</t>
+          <t>223192943</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>7,243,965,563</t>
+          <t>13,766,027,280</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>61.65</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>61.40</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>61.70</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>+1.20</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>69,793</t>
+          <t>277,389</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>114/10/17</t>
+          <t>114/11/17</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>166191884</t>
+          <t>91925734</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>10,319,476,518</t>
+          <t>5,696,893,851</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>62.05</t>
+          <t>62.00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>62.30</t>
+          <t>62.20</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
+          <t>61.80</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
           <t>61.90</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>62.05</t>
-        </is>
-      </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>+0.20</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>150,480</t>
+          <t>85,395</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>114/10/20</t>
+          <t>114/11/18</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>105854638</t>
+          <t>264956405</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>6,661,383,731</t>
+          <t>16,077,471,840</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>61.30</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>61.30</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>62.15</t>
+          <t>60.30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>63.10</t>
+          <t>60.45</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>+1.05</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>71,439</t>
+          <t>354,183</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>114/10/21</t>
+          <t>114/11/19</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>128793394</t>
+          <t>151383859</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>8,163,510,301</t>
+          <t>9,097,742,490</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>63.40</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>63.65</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>63.05</t>
+          <t>59.90</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>60.05</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>+0.10</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>81,028</t>
+          <t>198,226</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>114/10/22</t>
+          <t>114/11/20</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>124303290</t>
+          <t>84027889</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>7,767,140,110</t>
+          <t>5,187,294,354</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>62.60</t>
+          <t>61.55</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>62.85</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>62.25</t>
+          <t>61.35</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>62.70</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>+1.85</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>129,615</t>
+          <t>61,552</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>114/10/23</t>
+          <t>114/11/21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>166688171</t>
+          <t>327691489</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>10,363,437,208</t>
+          <t>19,593,794,724</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.75</t>
+          <t>59.50</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>59.85</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>93,117</t>
+          <t>410,104</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>114/10/27</t>
+          <t>114/11/24</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>104776108</t>
+          <t>162722018</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6,669,961,671</t>
+          <t>9,712,201,417</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>63.75</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>63.90</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>63.45</t>
+          <t>59.45</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>63.80</t>
+          <t>59.55</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>+1.45</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>64,536</t>
+          <t>155,513</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>114/10/28</t>
+          <t>114/11/25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>99770041</t>
+          <t>64411018</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6,330,563,186</t>
+          <t>3,893,075,835</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>63.55</t>
+          <t>60.70</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>60.75</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>63.35</t>
+          <t>60.35</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>+0.80</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>102,903</t>
+          <t>51,135</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>114/10/29</t>
+          <t>114/11/26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>67414369</t>
+          <t>75793554</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4,326,680,379</t>
+          <t>4,646,516,112</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>61.10</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>64.45</t>
+          <t>61.50</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>64.40</t>
+          <t>61.35</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>+1.05</t>
+          <t>+1.00</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>50,482</t>
+          <t>49,069</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>114/10/30</t>
+          <t>114/11/27</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>95106510</t>
+          <t>53852335</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6,125,525,659</t>
+          <t>3,333,400,290</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>64.60</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>64.80</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>64.00</t>
+          <t>61.65</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>64.40</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+0.55</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>77,635</t>
+          <t>39,232</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>114/10/31</t>
+          <t>114/11/28</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>55956524</t>
+          <t>68386478</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>3,616,991,558</t>
+          <t>4,252,497,861</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>64.60</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>64.80</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>64.40</t>
+          <t>61.85</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>64.75</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>+0.35</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>44,302</t>
+          <t>37,281</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>114/11/03</t>
+          <t>114/12/01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>140157410</t>
+          <t>103003085</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>9,004,715,647</t>
+          <t>6,350,023,506</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>64.45</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>64.80</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>63.90</t>
+          <t>61.40</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>64.15</t>
+          <t>61.50</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>154,188</t>
+          <t>105,261</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>114/11/04</t>
+          <t>114/12/02</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>88131032</t>
+          <t>43152711</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>5,658,007,897</t>
+          <t>2,670,762,886</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>64.50</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>64.85</t>
+          <t>62.20</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>63.85</t>
+          <t>61.65</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>61.70</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>+0.20</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>90,876</t>
+          <t>33,675</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>114/11/05</t>
+          <t>114/12/03</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>229413552</t>
+          <t>46546830</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>14,391,151,897</t>
+          <t>2,900,511,764</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>62.10</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>62.30</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>63.15</t>
-        </is>
-      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>+0.60</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>276,109</t>
+          <t>34,300</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>114/11/06</t>
+          <t>114/12/04</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>68680372</t>
+          <t>40655322</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>4,349,732,858</t>
+          <t>2,530,843,780</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>63.35</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>63.50</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>62.00</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>63.30</t>
+          <t>62.20</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>57,358</t>
+          <t>35,535</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>114/11/07</t>
+          <t>114/12/05</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>111187957</t>
+          <t>47277037</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>6,952,850,646</t>
+          <t>2,958,378,181</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>62.65</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4686,432 +4686,432 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>62.55</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.55</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>136,880</t>
+          <t>44,751</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>114/11/10</t>
+          <t>114/12/08</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>83130868</t>
+          <t>78686347</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>5,234,605,606</t>
+          <t>4,991,038,407</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>62.80</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>63.35</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>62.60</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>63.35</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>+0.80</t>
+          <t>+0.95</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>61,928</t>
+          <t>60,124</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>114/11/11</t>
+          <t>114/12/09</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>79723934</t>
+          <t>50671148</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>5,046,877,473</t>
+          <t>3,225,750,796</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>63.65</t>
+          <t>63.80</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>63.85</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>62.85</t>
+          <t>63.55</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>62.90</t>
+          <t>63.60</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>85,077</t>
+          <t>49,273</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>114/11/12</t>
+          <t>114/12/10</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>62620173</t>
+          <t>66717948</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>3,947,348,693</t>
+          <t>4,264,783,464</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>63.30</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>63.65</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>64.05</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>+0.30</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>55,267</t>
+          <t>51,254</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>114/11/13</t>
+          <t>114/12/11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>80483242</t>
+          <t>101197570</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>5,053,859,324</t>
+          <t>6,442,627,838</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>62.80</t>
+          <t>64.30</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>64.50</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>62.60</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>62.90</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>89,344</t>
+          <t>110,925</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>114/11/14</t>
+          <t>114/12/12</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>223192943</t>
+          <t>60240146</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>13,766,027,280</t>
+          <t>3,825,611,936</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>61.65</t>
+          <t>63.55</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>61.90</t>
+          <t>63.80</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.40</t>
+          <t>63.30</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>61.70</t>
+          <t>63.45</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>+0.10</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>277,389</t>
+          <t>49,189</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>114/11/17</t>
+          <t>114/12/15</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>91925734</t>
+          <t>114939409</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>5,696,893,851</t>
+          <t>7,203,513,013</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>62.00</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>62.20</t>
+          <t>62.85</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>61.90</t>
+          <t>62.80</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>+0.20</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>85,395</t>
+          <t>134,546</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>114/11/18</t>
+          <t>114/12/16</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>264956405</t>
+          <t>169375708</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>16,077,471,840</t>
+          <t>10,494,294,870</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>61.30</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>61.30</t>
+          <t>62.25</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>60.30</t>
+          <t>61.70</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>60.45</t>
+          <t>62.25</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>354,183</t>
+          <t>211,332</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>114/11/19</t>
+          <t>114/12/17</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>151383859</t>
+          <t>98504980</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>9,097,742,490</t>
+          <t>6,122,747,371</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>62.15</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>60.50</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>59.90</t>
+          <t>61.85</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>60.05</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>198,226</t>
+          <t>86,356</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>114/11/20</t>
+          <t>114/12/18</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>84027889</t>
+          <t>117973409</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>5,187,294,354</t>
+          <t>7,287,940,742</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t>61.80</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>62.10</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>61.55</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>61.95</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>61.35</t>
-        </is>
-      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>61.90</t>
@@ -5119,237 +5119,237 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>+1.85</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>61,552</t>
+          <t>87,078</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>114/11/21</t>
+          <t>114/12/19</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>327691489</t>
+          <t>81027467</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>19,593,794,724</t>
+          <t>5,067,295,440</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>60.10</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>59.50</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>+0.60</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>410,104</t>
+          <t>41,675</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>114/11/24</t>
+          <t>114/12/22</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>162722018</t>
+          <t>93882538</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>9,712,201,417</t>
+          <t>5,942,586,403</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>60.10</t>
+          <t>63.30</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>60.10</t>
+          <t>63.45</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>59.45</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>59.55</t>
+          <t>63.40</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>+0.90</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>155,513</t>
+          <t>52,777</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>114/11/25</t>
+          <t>114/12/23</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>64411018</t>
+          <t>101867829</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3,893,075,835</t>
+          <t>6,483,053,926</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>60.70</t>
+          <t>63.50</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>60.75</t>
+          <t>63.80</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>60.10</t>
+          <t>63.50</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>60.35</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>+0.80</t>
+          <t>+0.30</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>51,135</t>
+          <t>44,429</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>114/11/26</t>
+          <t>114/12/24</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>75793554</t>
+          <t>64106420</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4,646,516,112</t>
+          <t>4,094,914,827</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>61.10</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>61.50</t>
+          <t>64.05</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.00</t>
+          <t>63.75</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>61.35</t>
+          <t>63.85</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>+1.00</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>49,069</t>
+          <t>41,909</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>114/11/27</t>
+          <t>114/12/26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>53852335</t>
+          <t>70816194</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3,333,400,290</t>
+          <t>4,556,213,637</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>64.50</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.65</t>
+          <t>64.10</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>61.90</t>
+          <t>64.40</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5359,5786 +5359,4846 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>39,232</t>
+          <t>54,305</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>114/11/28</t>
+          <t>114/12/29</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>68386478</t>
+          <t>86510015</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>4,252,497,861</t>
+          <t>5,628,464,300</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>64.65</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>65.35</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.85</t>
+          <t>64.60</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>65.25</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>+0.85</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>37,281</t>
+          <t>63,528</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>114/12/01</t>
+          <t>114/12/30</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>103003085</t>
+          <t>61058197</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>6,350,023,506</t>
+          <t>3,970,585,296</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>64.90</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>65.30</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.40</t>
+          <t>64.75</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>61.50</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>105,261</t>
+          <t>54,458</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>114/12/02</t>
+          <t>114/12/31</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>43152711</t>
+          <t>71868485</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2,670,762,886</t>
+          <t>4,709,518,474</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>65.10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>62.20</t>
+          <t>65.85</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.65</t>
+          <t>64.90</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>61.70</t>
+          <t>65.60</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>+0.20</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>33,675</t>
+          <t>52,512</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>114/12/03</t>
+          <t>115/01/02</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>46546830</t>
+          <t>81135717</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2,900,511,764</t>
+          <t>5,396,295,605</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>66.00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>67.00</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>65.80</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>62.30</t>
+          <t>66.95</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>+0.60</t>
+          <t>+1.35</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>34,300</t>
+          <t>69,896</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>114/12/04</t>
+          <t>115/01/05</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>40655322</t>
+          <t>232910010</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2,530,843,780</t>
+          <t>16,163,783,922</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>68.10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>62.00</t>
+          <t>68.05</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>62.20</t>
+          <t>69.50</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+2.55</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>35,535</t>
+          <t>141,745</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>114/12/05</t>
+          <t>115/01/06</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>47277037</t>
+          <t>130176548</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2,958,378,181</t>
+          <t>9,090,693,014</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>62.45</t>
+          <t>69.45</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>70.40</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>68.95</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>70.40</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>+0.55</t>
+          <t>+0.90</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>44,751</t>
+          <t>94,772</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>114/12/08</t>
+          <t>115/01/07</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>78686347</t>
+          <t>122267721</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>4,991,038,407</t>
+          <t>8,554,349,889</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>70.40</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>+0.95</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>60,124</t>
+          <t>132,657</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>114/12/09</t>
+          <t>115/01/08</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>50671148</t>
+          <t>74866080</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3,225,750,796</t>
+          <t>5,233,314,685</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>63.80</t>
+          <t>69.65</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>63.85</t>
+          <t>70.35</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>63.55</t>
+          <t>69.40</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>63.60</t>
+          <t>70.10</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>49,273</t>
+          <t>65,275</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>114/12/10</t>
+          <t>115/01/09</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>66717948</t>
+          <t>113278257</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>4,264,783,464</t>
+          <t>7,882,596,065</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>69.80</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>63.65</t>
+          <t>68.90</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>64.05</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>51,254</t>
+          <t>117,481</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>114/12/11</t>
+          <t>115/01/12</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>101197570</t>
+          <t>84346348</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>6,442,627,838</t>
+          <t>5,928,941,344</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>64.30</t>
+          <t>70.50</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>64.50</t>
+          <t>70.55</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>63.35</t>
+          <t>70.35</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>+0.50</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>110,925</t>
+          <t>74,258</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>114/12/12</t>
+          <t>115/01/13</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>60240146</t>
+          <t>103565147</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3,825,611,936</t>
+          <t>7,323,170,787</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>63.55</t>
+          <t>71.10</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>63.80</t>
+          <t>71.20</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>63.30</t>
+          <t>70.30</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>63.45</t>
+          <t>70.70</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>+0.10</t>
+          <t>+0.35</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>49,189</t>
+          <t>77,504</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>114/12/15</t>
+          <t>115/01/14</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>114939409</t>
+          <t>86322515</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>7,203,513,013</t>
+          <t>6,115,431,229</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>70.95</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>62.85</t>
+          <t>71.10</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>70.65</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>62.80</t>
+          <t>70.75</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>134,546</t>
+          <t>67,445</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>114/12/16</t>
+          <t>115/01/15</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>169375708</t>
+          <t>97455363</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>10,494,294,870</t>
+          <t>6,856,607,422</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>70.70</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>62.25</t>
+          <t>70.70</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.70</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>62.25</t>
+          <t>70.65</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>211,332</t>
+          <t>122,171</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>114/12/17</t>
+          <t>115/01/16</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>98504980</t>
+          <t>101069992</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>6,122,747,371</t>
+          <t>7,242,693,243</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>62.15</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>62.45</t>
+          <t>72.10</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>61.85</t>
+          <t>71.20</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>61.90</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>+1.35</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>86,356</t>
+          <t>80,151</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>114/12/18</t>
+          <t>115/01/19</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>117973409</t>
+          <t>122970595</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>7,287,940,742</t>
+          <t>8,839,245,132</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>72.80</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.55</t>
+          <t>71.45</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>61.90</t>
+          <t>72.60</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+0.60</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>87,078</t>
+          <t>107,729</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>114/12/19</t>
+          <t>115/01/20</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>81027467</t>
+          <t>111046335</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>5,067,295,440</t>
+          <t>8,024,448,821</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>71.90</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>72.65</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>72.60</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>+0.60</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>41,675</t>
+          <t>99,563</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>114/12/22</t>
+          <t>115/01/21</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>93882538</t>
+          <t>173683092</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>5,942,586,403</t>
+          <t>12,502,883,011</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>63.30</t>
+          <t>71.80</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>63.45</t>
+          <t>72.50</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>63.05</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>63.40</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>+0.90</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>52,777</t>
+          <t>203,410</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>114/12/23</t>
+          <t>115/01/22</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>101867829</t>
+          <t>101703005</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>6,483,053,926</t>
+          <t>7,306,066,892</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>63.50</t>
+          <t>71.90</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>63.80</t>
+          <t>72.05</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>63.50</t>
+          <t>71.60</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>71.80</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>+0.30</t>
+          <t>X0.00</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>44,429</t>
+          <t>92,128</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>114/12/24</t>
+          <t>115/01/23</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>64106420</t>
+          <t>70983017</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>4,094,914,827</t>
+          <t>5,116,365,718</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>72.10</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>64.05</t>
+          <t>72.30</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>63.75</t>
+          <t>71.80</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>63.85</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>41,909</t>
+          <t>49,675</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>114/12/26</t>
+          <t>115/01/26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>70816194</t>
+          <t>87992466</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>4,556,213,637</t>
+          <t>6,373,835,828</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>64.50</t>
+          <t>72.65</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>64.10</t>
+          <t>72.20</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>64.40</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>+0.55</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>54,305</t>
+          <t>72,487</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>114/12/29</t>
+          <t>115/01/27</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>86510015</t>
+          <t>73059634</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>5,628,464,300</t>
+          <t>5,322,600,617</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>64.65</t>
+          <t>72.40</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>65.35</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>64.60</t>
+          <t>72.35</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>65.25</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>+0.85</t>
+          <t>+0.80</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>63,528</t>
+          <t>53,680</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>114/12/30</t>
+          <t>115/01/28</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>61058197</t>
+          <t>90901846</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>3,970,585,296</t>
+          <t>6,711,076,738</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>64.90</t>
+          <t>73.55</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>65.30</t>
+          <t>74.20</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>64.75</t>
+          <t>73.50</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>74.20</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+1.15</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>54,458</t>
+          <t>67,825</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>114/12/31</t>
+          <t>115/01/29</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>71868485</t>
+          <t>119914950</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>4,709,518,474</t>
+          <t>8,867,286,368</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>65.10</t>
+          <t>74.40</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>74.50</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>64.90</t>
+          <t>73.50</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>65.60</t>
+          <t>73.75</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>52,512</t>
+          <t>121,772</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>115/01/02</t>
+          <t>115/01/30</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>81135717</t>
+          <t>175275799</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>5,396,295,605</t>
+          <t>12,738,811,404</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>66.00</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>67.00</t>
+          <t>73.20</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>65.80</t>
+          <t>72.30</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>72.60</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>+1.35</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>69,896</t>
+          <t>241,546</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>115/01/05</t>
+          <t>115/02/02</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>232910010</t>
+          <t>234325396</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>16,163,783,922</t>
+          <t>16,687,566,456</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>68.10</t>
+          <t>71.55</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>68.05</t>
+          <t>70.90</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>69.50</t>
+          <t>71.50</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>+2.55</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>141,745</t>
+          <t>332,048</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>115/01/06</t>
+          <t>115/02/03</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>130176548</t>
+          <t>73734001</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>9,090,693,014</t>
+          <t>5,367,935,502</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>69.45</t>
+          <t>73.00</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>70.40</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>68.95</t>
+          <t>72.40</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>70.40</t>
+          <t>72.95</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>+0.90</t>
+          <t>+1.45</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>94,772</t>
+          <t>60,314</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>115/01/07</t>
+          <t>115/02/04</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>122267721</t>
+          <t>59733704</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>8,554,349,889</t>
+          <t>4,346,370,749</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>70.40</t>
+          <t>72.40</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.70</t>
+          <t>72.30</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>72.90</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>132,657</t>
+          <t>55,518</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>115/01/08</t>
+          <t>115/02/05</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>74866080</t>
+          <t>107575796</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>5,233,314,685</t>
+          <t>7,742,810,789</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>69.65</t>
+          <t>72.05</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>69.40</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>70.10</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>65,275</t>
+          <t>175,926</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>115/01/09</t>
+          <t>115/02/06</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>113278257</t>
+          <t>110883112</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>7,882,596,065</t>
+          <t>7,920,520,483</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>69.80</t>
+          <t>71.40</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>68.90</t>
+          <t>70.80</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>71.90</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>117,481</t>
+          <t>134,413</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>115/01/12</t>
+          <t>115/02/09</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>84346348</t>
+          <t>122340661</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>5,928,941,344</t>
+          <t>9,050,873,718</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>70.50</t>
+          <t>74.05</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>70.55</t>
+          <t>74.15</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>73.75</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>+0.50</t>
+          <t>+2.05</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>74,258</t>
+          <t>81,342</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>115/01/13</t>
+          <t>115/02/10</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>103565147</t>
+          <t>102315945</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>7,323,170,787</t>
+          <t>7,703,131,124</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>71.10</t>
+          <t>74.65</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>71.20</t>
+          <t>75.50</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>70.30</t>
+          <t>74.60</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>70.70</t>
+          <t>75.50</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>+0.35</t>
+          <t>+1.55</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>77,504</t>
+          <t>80,773</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>115/01/14</t>
+          <t>115/02/11</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>86322515</t>
+          <t>120639150</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>6,115,431,229</t>
+          <t>9,275,271,308</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>70.95</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>71.10</t>
+          <t>77.45</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>70.65</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>70.75</t>
+          <t>77.20</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>+0.05</t>
+          <t>+1.70</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>67,445</t>
+          <t>118,568</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>115/01/15</t>
+          <t>115/02/23</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>97455363</t>
+          <t>227936939</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>6,856,607,422</t>
+          <t>17,749,552,954</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>70.70</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>70.70</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>77.20</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>70.65</t>
+          <t>77.40</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+0.20</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>122,171</t>
+          <t>220,396</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>115/01/16</t>
+          <t>115/02/24</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>101069992</t>
+          <t>150367766</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>7,242,693,243</t>
+          <t>11,848,589,798</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>77.95</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>72.10</t>
+          <t>79.65</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>71.20</t>
+          <t>77.85</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>79.40</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>+1.35</t>
+          <t>+2.00</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>80,151</t>
+          <t>117,830</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>115/01/19</t>
+          <t>115/02/25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>122970595</t>
+          <t>167423484</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>8,839,245,132</t>
+          <t>13,565,896,459</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>72.80</t>
+          <t>81.80</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>72.60</t>
+          <t>81.10</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>+0.60</t>
+          <t>+1.70</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>107,729</t>
+          <t>141,615</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>115/01/20</t>
+          <t>115/02/26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>111046335</t>
+          <t>133517321</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>8,024,448,821</t>
+          <t>10,841,079,880</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>71.90</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>72.65</t>
+          <t>81.50</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>80.80</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>72.60</t>
+          <t>81.15</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>99,563</t>
+          <t>133,768</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>115/01/21</t>
+          <t>115/03/02</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>173683092</t>
+          <t>224651381</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>12,502,883,011</t>
+          <t>18,053,460,439</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>71.80</t>
+          <t>79.50</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>72.50</t>
+          <t>80.80</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>79.15</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>203,410</t>
+          <t>297,372</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>115/01/22</t>
+          <t>115/03/03</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>101703005</t>
+          <t>324317518</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>7,306,066,892</t>
+          <t>25,713,110,082</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>71.90</t>
+          <t>80.05</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>72.05</t>
+          <t>80.40</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>71.60</t>
+          <t>78.65</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>71.80</t>
+          <t>78.75</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>X0.00</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>92,128</t>
+          <t>516,152</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>115/01/23</t>
+          <t>115/03/04</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>70983017</t>
+          <t>505217770</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>5,116,365,718</t>
+          <t>38,471,650,068</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>72.10</t>
+          <t>77.40</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>72.30</t>
+          <t>77.45</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>71.80</t>
+          <t>75.50</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>49,675</t>
+          <t>711,329</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>115/01/26</t>
+          <t>115/03/05</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>87992466</t>
+          <t>207004644</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>6,373,835,828</t>
+          <t>16,090,040,992</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>72.65</t>
+          <t>78.85</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>76.70</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>77.40</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+1.80</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>72,487</t>
+          <t>204,272</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>115/01/27</t>
+          <t>115/03/06</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>73059634</t>
+          <t>151611764</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>5,322,600,617</t>
+          <t>11,638,160,681</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>72.40</t>
+          <t>76.80</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>77.30</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>76.85</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>+0.80</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>53,680</t>
+          <t>179,651</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>115/01/28</t>
+          <t>115/03/09</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>90901846</t>
+          <t>542230074</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>6,711,076,738</t>
+          <t>39,488,306,757</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>73.55</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>74.20</t>
+          <t>73.60</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>73.50</t>
+          <t>71.65</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>74.20</t>
+          <t>73.60</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>+1.15</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>67,825</t>
+          <t>658,991</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>115/01/29</t>
+          <t>115/03/10</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>119914950</t>
+          <t>173870150</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>8,867,286,368</t>
+          <t>13,134,447,601</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>74.40</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>74.50</t>
+          <t>76.25</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>73.50</t>
+          <t>74.30</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>75.20</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>+1.60</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>121,772</t>
+          <t>180,826</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>115/01/30</t>
+          <t>115/03/11</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>175275799</t>
+          <t>151798656</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>12,738,811,404</t>
+          <t>11,785,499,671</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>73.20</t>
+          <t>78.50</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>72.30</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>72.60</t>
+          <t>78.20</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>+3.00</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>241,546</t>
+          <t>104,693</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>115/02/02</t>
+          <t>115/03/12</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>234325396</t>
+          <t>131518817</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>16,687,566,456</t>
+          <t>10,107,953,882</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>71.55</t>
+          <t>77.10</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>77.60</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>70.90</t>
+          <t>76.35</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>71.50</t>
+          <t>76.60</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>332,048</t>
+          <t>180,533</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>115/02/03</t>
+          <t>115/03/13</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>73734001</t>
+          <t>115111624</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>5,367,935,502</t>
+          <t>8,723,084,020</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>73.00</t>
+          <t>75.15</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>76.55</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>72.40</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>72.95</t>
+          <t>75.95</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>+1.45</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>60,314</t>
+          <t>160,164</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>115/02/04</t>
+          <t>115/03/16</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>59733704</t>
+          <t>105392137</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>4,346,370,749</t>
+          <t>7,994,232,270</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>72.40</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>76.70</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>72.30</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>72.90</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>55,518</t>
+          <t>135,317</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>115/02/05</t>
+          <t>115/03/17</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>107575796</t>
+          <t>63986997</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>7,742,810,789</t>
+          <t>4,901,077,314</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>72.05</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>77.00</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>76.65</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>+1.05</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>175,926</t>
+          <t>54,634</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>115/02/06</t>
+          <t>115/03/18</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>110883112</t>
+          <t>78000193</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>7,920,520,483</t>
+          <t>6,064,253,100</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>71.40</t>
+          <t>77.75</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>78.05</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>70.80</t>
+          <t>77.45</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>71.90</t>
+          <t>77.80</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+1.15</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>134,413</t>
+          <t>65,062</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>115/02/09</t>
+          <t>115/03/19</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>122340661</t>
+          <t>141733755</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>9,050,873,718</t>
+          <t>10,821,638,440</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>74.05</t>
+          <t>76.60</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>74.15</t>
+          <t>76.80</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>75.95</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>76.00</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>+2.05</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>81,342</t>
+          <t>218,952</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>115/02/10</t>
+          <t>115/03/20</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>102315945</t>
+          <t>72638922</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>7,703,131,124</t>
+          <t>5,517,624,557</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>74.65</t>
+          <t>76.20</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
+          <t>76.40</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
           <t>75.50</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>74.60</t>
-        </is>
-      </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>+1.55</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>80,773</t>
+          <t>101,109</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>115/02/11</t>
+          <t>115/03/23</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>120639150</t>
+          <t>233385121</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>9,275,271,308</t>
+          <t>17,256,278,289</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>73.50</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>77.45</t>
+          <t>74.45</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>73.30</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>77.20</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>+1.70</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>118,568</t>
+          <t>340,169</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>115/02/23</t>
+          <t>115/03/24</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>227936939</t>
+          <t>90466270</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>17,749,552,954</t>
+          <t>6,750,345,110</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>75.50</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>77.20</t>
+          <t>73.80</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>77.40</t>
+          <t>74.40</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>+0.20</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>220,396</t>
+          <t>111,636</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>115/02/24</t>
+          <t>115/03/25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>150367766</t>
+          <t>94344080</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>11,848,589,798</t>
+          <t>7,201,277,589</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>77.95</t>
+          <t>76.35</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>79.65</t>
+          <t>76.65</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>77.85</t>
+          <t>76.00</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>79.40</t>
+          <t>76.20</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>+2.00</t>
+          <t>+1.80</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>117,830</t>
+          <t>66,655</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>115/02/25</t>
+          <t>115/03/26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>167423484</t>
+          <t>80069071</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>13,565,896,459</t>
+          <t>6,102,674,371</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>81.80</t>
+          <t>76.85</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>81.10</t>
+          <t>75.80</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>+1.70</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>141,615</t>
+          <t>80,270</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>115/02/26</t>
+          <t>115/03/27</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>133517321</t>
+          <t>115798710</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>10,841,079,880</t>
+          <t>8,622,872,378</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>74.45</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>81.50</t>
+          <t>75.10</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>80.80</t>
+          <t>74.10</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>81.15</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>+0.05</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>133,768</t>
+          <t>161,501</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>115/03/02</t>
+          <t>115/03/30</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>224651381</t>
+          <t>175515568</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>18,053,460,439</t>
+          <t>12,905,676,995</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>79.50</t>
+          <t>73.30</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>80.80</t>
+          <t>74.05</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>79.15</t>
+          <t>72.80</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>297,372</t>
+          <t>261,697</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>115/03/03</t>
+          <t>115/03/31</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>324317518</t>
+          <t>257738774</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>25,713,110,082</t>
+          <t>18,741,416,482</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>80.05</t>
+          <t>73.35</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>80.40</t>
+          <t>73.45</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>78.65</t>
+          <t>72.15</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>72.35</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>516,152</t>
+          <t>400,630</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>115/03/04</t>
+          <t>115/04/01</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>505217770</t>
+          <t>130698663</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>38,471,650,068</t>
+          <t>9,824,716,760</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>77.40</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>77.45</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>74.60</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>+3.10</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>711,329</t>
+          <t>89,221</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>115/03/05</t>
+          <t>115/04/02</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>207004644</t>
+          <t>113976137</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>16,090,040,992</t>
+          <t>8,478,357,215</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>78.30</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>78.85</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>76.70</t>
+          <t>73.80</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>77.40</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>+1.80</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>204,272</t>
+          <t>162,558</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>115/03/06</t>
+          <t>115/04/07</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>151611764</t>
+          <t>80449813</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>11,638,160,681</t>
+          <t>6,046,717,969</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>76.80</t>
+          <t>75.15</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>77.30</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>74.65</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>76.85</t>
+          <t>75.30</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>+1.35</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>179,651</t>
+          <t>81,117</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>115/03/09</t>
+          <t>115/04/08</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>542230074</t>
+          <t>235675856</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>39,488,306,757</t>
+          <t>18,578,257,980</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>78.10</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>73.60</t>
+          <t>79.25</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>71.65</t>
+          <t>78.10</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>73.60</t>
+          <t>79.20</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>+3.90</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>658,991</t>
+          <t>148,473</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>115/03/10</t>
+          <t>115/04/09</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>173870150</t>
+          <t>95094893</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>13,134,447,601</t>
+          <t>7,520,522,079</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>79.30</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>79.40</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>74.30</t>
+          <t>78.80</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>75.20</t>
+          <t>79.15</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>+1.60</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>180,826</t>
+          <t>72,839</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>115/03/11</t>
+          <t>115/04/10</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>151798656</t>
+          <t>120838644</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>11,785,499,671</t>
+          <t>9,724,171,699</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>78.50</t>
+          <t>80.80</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>79.95</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>78.20</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>+3.00</t>
+          <t>+1.60</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>104,693</t>
+          <t>98,770</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>115/03/12</t>
+          <t>115/04/13</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>131518817</t>
+          <t>91689847</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>10,107,953,882</t>
+          <t>7,398,471,916</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>77.10</t>
+          <t>80.60</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>77.60</t>
+          <t>81.00</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>76.35</t>
+          <t>80.40</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>76.60</t>
+          <t>80.60</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>180,533</t>
+          <t>86,103</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>115/03/13</t>
+          <t>115/04/14</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>115111624</t>
+          <t>129128623</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>8,723,084,020</t>
+          <t>10,668,730,259</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>75.15</t>
+          <t>81.75</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>76.55</t>
+          <t>83.20</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>81.75</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>75.95</t>
+          <t>83.10</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>+2.50</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>160,164</t>
+          <t>101,069</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>115/03/16</t>
+          <t>115/04/15</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>105392137</t>
+          <t>127729350</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>7,994,232,270</t>
+          <t>10,793,181,456</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>84.10</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>76.70</t>
+          <t>85.10</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>75.45</t>
+          <t>83.80</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>+1.05</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>135,317</t>
+          <t>122,459</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>115/03/17</t>
+          <t>115/04/16</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>63986997</t>
+          <t>80696269</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>4,901,077,314</t>
+          <t>6,829,488,057</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>77.00</t>
+          <t>85.10</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>76.65</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>+1.05</t>
+          <t>+0.85</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>54,634</t>
+          <t>78,794</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>115/03/18</t>
+          <t>115/04/17</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>78000193</t>
+          <t>101258031</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>6,064,253,100</t>
+          <t>8,526,065,307</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>77.75</t>
+          <t>84.20</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>78.05</t>
+          <t>84.50</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>77.45</t>
+          <t>84.00</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>77.80</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>+1.15</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>65,062</t>
+          <t>146,785</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>115/03/19</t>
+          <t>115/04/20</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>141733755</t>
+          <t>100551500</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>10,821,638,440</t>
+          <t>8,533,691,370</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>76.60</t>
+          <t>84.55</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>76.80</t>
+          <t>85.10</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>75.95</t>
+          <t>84.45</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>76.00</t>
+          <t>84.55</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>+0.40</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>218,952</t>
+          <t>90,566</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>115/03/20</t>
+          <t>115/04/21</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>72638922</t>
+          <t>75557759</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>5,517,624,557</t>
+          <t>6,477,242,890</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>76.20</t>
+          <t>85.50</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>76.40</t>
+          <t>86.10</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>86.00</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+1.45</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>101,109</t>
+          <t>72,495</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>115/03/23</t>
+          <t>115/04/22</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>233385121</t>
+          <t>67544248</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>17,256,278,289</t>
+          <t>5,828,004,375</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>73.50</t>
+          <t>85.75</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>74.45</t>
+          <t>86.60</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>73.30</t>
+          <t>85.55</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>86.35</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>+0.35</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>340,169</t>
+          <t>70,385</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>115/03/24</t>
+          <t>115/04/23</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>90466270</t>
+          <t>156715780</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>6,750,345,110</t>
+          <t>13,599,617,688</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>87.65</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>88.80</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>73.80</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>74.40</t>
+          <t>86.35</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>111,636</t>
+          <t>161,030</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>115/03/25</t>
+          <t>115/04/24</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>94344080</t>
+          <t>129885911</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>7,201,277,589</t>
+          <t>11,539,759,376</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>76.35</t>
+          <t>87.60</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>76.65</t>
+          <t>89.95</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>76.00</t>
+          <t>87.55</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>76.20</t>
+          <t>89.95</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>+1.80</t>
+          <t>+3.60</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>66,655</t>
+          <t>99,531</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>115/03/26</t>
+          <t>115/04/27</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>80069071</t>
+          <t>192038103</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>6,102,674,371</t>
+          <t>17,927,615,310</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>92.70</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>76.85</t>
+          <t>94.25</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>92.70</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>75.80</t>
+          <t>93.00</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>+3.05</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>80,270</t>
+          <t>172,215</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>115/03/27</t>
+          <t>115/04/28</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>115798710</t>
+          <t>126301332</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>8,622,872,378</t>
+          <t>11,691,553,456</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>74.45</t>
+          <t>92.55</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>75.10</t>
+          <t>93.65</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>74.10</t>
+          <t>91.90</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>92.00</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>161,501</t>
+          <t>193,633</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>115/03/30</t>
+          <t>115/04/29</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>175515568</t>
+          <t>103795530</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>12,905,676,995</t>
+          <t>9,410,136,420</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>73.30</t>
+          <t>90.70</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>74.05</t>
+          <t>91.50</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>72.80</t>
+          <t>90.00</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>261,697</t>
+          <t>163,856</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>115/03/31</t>
+          <t>115/04/30</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>257738774</t>
+          <t>89209769</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>18,741,416,482</t>
+          <t>8,111,730,781</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>73.35</t>
+          <t>91.25</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>73.45</t>
+          <t>91.90</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>72.15</t>
+          <t>90.30</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>90.50</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>400,630</t>
+          <t>125,264</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>115/04/01</t>
+          <t>115/05/04</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>130698663</t>
+          <t>125270935</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>9,824,716,760</t>
+          <t>11,748,311,547</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>94.65</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>74.60</t>
+          <t>92.40</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>75.45</t>
+          <t>94.60</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>+3.10</t>
+          <t>+4.10</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>89,221</t>
+          <t>114,510</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>115/04/02</t>
+          <t>115/05/05</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>113976137</t>
+          <t>82851869</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>8,478,357,215</t>
+          <t>7,821,971,023</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>94.40</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>94.75</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>73.80</t>
+          <t>94.00</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>94.60</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>162,558</t>
+          <t>115,951</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>115/04/07</t>
+          <t>115/05/06</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>80449813</t>
+          <t>111759164</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>6,046,717,969</t>
+          <t>10,703,702,958</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>75.15</t>
+          <t>96.05</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>75.45</t>
+          <t>96.90</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>74.65</t>
+          <t>94.70</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>75.30</t>
+          <t>95.75</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>+1.35</t>
+          <t>+1.15</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>81,117</t>
+          <t>120,555</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>115/04/08</t>
+          <t>115/05/07</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>235675856</t>
+          <t>117152238</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>18,578,257,980</t>
+          <t>11,472,448,704</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>78.10</t>
+          <t>97.95</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>79.25</t>
+          <t>98.40</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>78.10</t>
+          <t>97.40</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>79.20</t>
+          <t>97.70</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>+3.90</t>
+          <t>+1.95</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>148,473</t>
+          <t>119,685</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>115/04/09</t>
+          <t>115/05/08</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>95094893</t>
+          <t>131188123</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>7,520,522,079</t>
+          <t>12,716,275,565</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>79.30</t>
+          <t>97.35</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>79.40</t>
+          <t>97.70</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>78.80</t>
+          <t>95.85</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>79.15</t>
+          <t>97.00</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>72,839</t>
+          <t>217,822</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>115/04/10</t>
+          <t>115/05/11</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>120838644</t>
+          <t>96606391</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>9,724,171,699</t>
+          <t>9,362,479,353</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>96.65</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>80.80</t>
+          <t>97.15</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>79.95</t>
+          <t>96.50</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>96.90</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>+1.60</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>98,770</t>
+          <t>148,902</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>115/04/13</t>
+          <t>115/05/12</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>91689847</t>
+          <t>102303450</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>7,398,471,916</t>
+          <t>9,876,959,425</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>80.60</t>
+          <t>96.85</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>81.00</t>
+          <t>97.35</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>80.40</t>
+          <t>95.50</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>80.60</t>
+          <t>96.85</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>86,103</t>
+          <t>142,949</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>115/04/14</t>
+          <t>115/05/13</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>129128623</t>
+          <t>130654061</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>10,668,730,259</t>
+          <t>12,419,149,243</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>81.75</t>
+          <t>94.85</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>83.20</t>
+          <t>95.80</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>81.75</t>
+          <t>94.70</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>83.10</t>
+          <t>95.50</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>+2.50</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>101,069</t>
+          <t>260,692</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>115/04/15</t>
+          <t>115/05/14</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>127729350</t>
+          <t>57229209</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>10,793,181,456</t>
+          <t>5,510,647,058</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>84.10</t>
+          <t>96.90</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>85.10</t>
+          <t>97.20</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>83.80</t>
+          <t>95.75</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>96.05</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>+1.05</t>
+          <t>+0.55</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>122,459</t>
+          <t>70,419</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>115/04/16</t>
+          <t>115/05/15</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>80696269</t>
+          <t>98132989</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>6,829,488,057</t>
+          <t>9,472,541,597</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>97.65</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>85.10</t>
+          <t>98.25</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>95.20</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>95.40</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>+0.85</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>78,794</t>
+          <t>144,425</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>115/04/17</t>
+          <t>115/05/18</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>101258031</t>
+          <t>118571453</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>8,526,065,307</t>
+          <t>11,160,721,206</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>84.20</t>
+          <t>94.00</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>84.50</t>
+          <t>95.20</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>84.00</t>
+          <t>93.30</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>94.90</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>146,785</t>
+          <t>219,202</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>115/04/20</t>
+          <t>115/05/19</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>100551500</t>
+          <t>135939820</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>8,533,691,370</t>
+          <t>12,740,872,880</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>84.55</t>
+          <t>94.35</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>85.10</t>
+          <t>94.70</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>84.45</t>
+          <t>93.10</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>84.55</t>
+          <t>93.10</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>+0.40</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>90,566</t>
+          <t>304,750</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>115/04/21</t>
+          <t>115/05/20</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>75557759</t>
+          <t>121650308</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>6,477,242,890</t>
+          <t>11,289,688,382</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>85.50</t>
+          <t>93.00</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>86.10</t>
+          <t>93.50</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>92.45</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>86.00</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>+1.45</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>72,495</t>
+          <t>227,369</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>115/04/22</t>
+          <t>115/05/21</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>67544248</t>
+          <t>62215954</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>5,828,004,375</t>
+          <t>5,942,503,747</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>85.75</t>
+          <t>94.80</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>96.05</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>85.55</t>
+          <t>94.70</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>86.35</t>
+          <t>95.85</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>+0.35</t>
+          <t>+3.35</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>70,385</t>
+          <t>64,187</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>115/04/23</t>
+          <t>115/05/22</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>156715780</t>
+          <t>64288280</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>13,599,617,688</t>
+          <t>6,213,742,970</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>87.65</t>
+          <t>96.30</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>88.80</t>
+          <t>97.30</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>96.00</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>86.35</t>
+          <t>97.30</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+1.45</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>161,030</t>
+          <t>70,101</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>115/04/24</t>
+          <t>115/05/25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>129885911</t>
+          <t>129483256</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>11,539,759,376</t>
+          <t>13,010,032,076</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>87.60</t>
+          <t>99.55</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>101.00</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>87.55</t>
+          <t>99.55</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>100.80</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>+3.60</t>
+          <t>+3.50</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>99,531</t>
+          <t>107,787</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>115/04/27</t>
+          <t>115/05/26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>192038103</t>
+          <t>93560313</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>17,927,615,310</t>
+          <t>9,432,115,613</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>92.70</t>
+          <t>101.60</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>101.80</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>92.70</t>
+          <t>100.10</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>93.00</t>
+          <t>100.10</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>+3.05</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>172,215</t>
+          <t>112,958</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>115/04/28</t>
+          <t>115/05/27</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>126301332</t>
+          <t>94959812</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>11,691,553,456</t>
+          <t>9,787,482,181</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>92.55</t>
+          <t>102.40</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>93.65</t>
+          <t>103.90</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>91.90</t>
+          <t>102.00</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>92.00</t>
+          <t>102.55</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>+2.45</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>193,633</t>
+          <t>98,413</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>115/04/29</t>
+          <t>115/05/28</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>103795530</t>
+          <t>152915695</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>9,410,136,420</t>
+          <t>15,600,509,184</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>90.70</t>
+          <t>104.00</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>91.50</t>
+          <t>104.25</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>90.00</t>
+          <t>100.10</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>90.75</t>
+          <t>100.50</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>163,856</t>
+          <t>207,536</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>115/04/30</t>
+          <t>115/05/29</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>89209769</t>
+          <t>102355526</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>8,111,730,781</t>
+          <t>10,636,250,508</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>91.25</t>
+          <t>103.20</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>91.90</t>
+          <t>105.40</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>90.30</t>
+          <t>102.70</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>90.50</t>
+          <t>105.40</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+4.90</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>125,264</t>
+          <t>80,065</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>115/05/04</t>
+          <t>115/06/01</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>125270935</t>
+          <t>135817122</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>11,748,311,547</t>
+          <t>14,329,024,058</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>92.50</t>
+          <t>105.25</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>94.65</t>
+          <t>106.70</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>92.40</t>
+          <t>104.50</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>94.60</t>
+          <t>105.50</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>+4.10</t>
+          <t>+0.10</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>114,510</t>
+          <t>156,361</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>115/05/05</t>
+          <t>115/06/02</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>82851869</t>
+          <t>117160979</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>7,821,971,023</t>
+          <t>12,341,210,929</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>94.40</t>
+          <t>106.30</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>94.75</t>
+          <t>106.30</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>94.00</t>
+          <t>104.20</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>94.60</t>
+          <t>105.70</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+0.20</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>115,951</t>
+          <t>164,814</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>115/05/06</t>
+          <t>115/06/03</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>111759164</t>
+          <t>79592362</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>10,703,702,958</t>
+          <t>8,559,208,311</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>96.05</t>
+          <t>107.30</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>96.90</t>
+          <t>107.85</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>94.70</t>
+          <t>107.10</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>95.75</t>
+          <t>107.60</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>+1.15</t>
+          <t>+1.90</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>120,555</t>
+          <t>86,991</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>115/05/07</t>
+          <t>115/06/04</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>117152238</t>
+          <t>236782252</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>11,472,448,704</t>
+          <t>25,181,889,523</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>97.95</t>
+          <t>106.75</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>98.40</t>
+          <t>107.00</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>97.40</t>
+          <t>106.05</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>97.70</t>
+          <t>106.10</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>+1.95</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>119,685</t>
+          <t>210,220</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>115/05/08</t>
+          <t>115/06/05</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>131188123</t>
+          <t>337031371</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>12,716,275,565</t>
+          <t>34,914,259,576</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>97.35</t>
+          <t>105.00</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>97.70</t>
+          <t>105.35</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>95.85</t>
+          <t>102.80</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>97.00</t>
+          <t>104.15</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
-        <is>
-          <t>217,822</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>115/05/11</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>96606391</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>9,362,479,353</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>96.65</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>97.15</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>96.50</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>96.90</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>148,902</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>115/05/12</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>102303450</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>9,876,959,425</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>96.85</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>97.35</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>95.50</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>96.85</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>142,949</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>115/05/13</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>130654061</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>12,419,149,243</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>94.85</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>95.80</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>94.70</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>95.50</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>260,692</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>115/05/14</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>57229209</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>5,510,647,058</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>96.90</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>97.20</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>95.75</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>96.05</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>+0.55</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>70,419</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>115/05/15</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>98132989</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>9,472,541,597</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>97.65</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>98.25</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>95.20</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>95.40</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>-0.65</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>144,425</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>115/05/18</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>118571453</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>11,160,721,206</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>94.00</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>95.20</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>93.30</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>94.90</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>-0.50</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>219,202</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>115/05/19</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>135939820</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>12,740,872,880</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>94.35</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>94.70</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>93.10</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>93.10</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>-1.80</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>304,750</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>115/05/20</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>121650308</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>11,289,688,382</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>93.00</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>93.50</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>92.45</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>227,369</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>115/05/21</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>62215954</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>5,942,503,747</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>94.80</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>96.05</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>94.70</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>95.85</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>+3.35</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>64,187</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>115/05/22</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>64288280</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>6,213,742,970</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>96.30</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>97.30</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>96.00</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>97.30</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>+1.45</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>70,101</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>115/05/25</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>129483256</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>13,010,032,076</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>99.55</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>99.55</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>100.80</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>+3.50</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>107,787</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>115/05/26</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>93560313</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>9,432,115,613</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>101.60</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>101.80</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>-0.70</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>112,958</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>115/05/27</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>94959812</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>9,787,482,181</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>102.40</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>103.90</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>102.00</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>102.55</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>+2.45</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>98,413</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>115/05/28</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>152915695</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>15,600,509,184</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>104.00</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>104.25</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>100.10</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>100.50</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>-2.05</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>207,536</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>115/05/29</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>102355526</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>10,636,250,508</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>103.20</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>105.40</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>102.70</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>105.40</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>+4.90</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>80,065</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>115/06/01</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>135817122</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>14,329,024,058</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>105.25</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>106.70</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>104.50</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>105.50</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>+0.10</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>156,361</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>115/06/02</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>117160979</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>12,341,210,929</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>106.30</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>106.30</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>104.20</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>105.70</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>+0.20</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>164,814</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>115/06/03</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>79592362</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>8,559,208,311</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>107.30</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>107.85</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>107.10</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>107.60</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>+1.90</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>86,991</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>115/06/04</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>236782252</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>25,181,889,523</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>106.75</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>107.00</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>106.05</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>106.10</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>-1.50</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>210,220</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>115/06/05</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>337031371</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>34,914,259,576</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>105.00</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>105.35</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>102.80</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>104.15</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
         <is>
           <t>355,384</t>
         </is>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I208"/>
+  <dimension ref="A1:I228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,1150 +3533,1150 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>114/11/03</t>
+          <t>114/10/01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>140157410</t>
+          <t>77291614</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>9,004,715,647</t>
+          <t>4,503,366,313</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>64.45</t>
+          <t>57.90</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>64.80</t>
+          <t>58.75</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>63.90</t>
+          <t>57.90</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>64.15</t>
+          <t>58.10</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>+0.30</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>154,188</t>
+          <t>59,386</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>114/11/04</t>
+          <t>114/10/02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>88131032</t>
+          <t>73803137</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>5,658,007,897</t>
+          <t>4,361,065,414</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>64.50</t>
+          <t>59.00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>64.85</t>
+          <t>59.25</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>63.85</t>
+          <t>58.85</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>59.20</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>+1.10</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>90,876</t>
+          <t>45,593</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>114/11/05</t>
+          <t>114/10/03</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>229413552</t>
+          <t>76083554</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>14,391,151,897</t>
+          <t>4,545,707,938</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>59.20</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>62.30</t>
+          <t>59.05</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>60.05</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>+0.85</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>276,109</t>
+          <t>58,010</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>114/11/06</t>
+          <t>114/10/07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>68680372</t>
+          <t>138001575</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>4,349,732,858</t>
+          <t>8,474,594,769</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>63.35</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>63.50</t>
+          <t>61.70</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>60.90</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>63.30</t>
+          <t>61.70</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>+1.65</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>57,358</t>
+          <t>98,359</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>114/11/07</t>
+          <t>114/10/08</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>111187957</t>
+          <t>119706336</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>6,952,850,646</t>
+          <t>7,282,646,193</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>62.65</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>61.15</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>60.60</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>62.55</t>
+          <t>61.15</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>136,880</t>
+          <t>117,731</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>114/11/10</t>
+          <t>114/10/09</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>83130868</t>
+          <t>76478634</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>5,234,605,606</t>
+          <t>4,720,554,315</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>62.80</t>
+          <t>61.85</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>63.35</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>62.60</t>
+          <t>61.50</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>63.35</t>
+          <t>61.60</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>+0.80</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>61,928</t>
+          <t>62,822</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>114/11/11</t>
+          <t>114/10/13</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>79723934</t>
+          <t>277610574</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>5,046,877,473</t>
+          <t>16,788,141,527</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>63.65</t>
+          <t>59.90</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>62.85</t>
+          <t>59.60</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>62.90</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>85,077</t>
+          <t>257,909</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>114/11/12</t>
+          <t>114/10/14</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>62620173</t>
+          <t>163441296</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>3,947,348,693</t>
+          <t>10,048,295,024</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>61.85</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>63.30</t>
+          <t>62.15</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>60.65</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>60.70</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>+0.30</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>55,267</t>
+          <t>129,817</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>114/11/13</t>
+          <t>114/10/15</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>80483242</t>
+          <t>101918261</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>5,053,859,324</t>
+          <t>6,245,523,944</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>62.80</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>62.60</t>
+          <t>60.60</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>62.90</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>+1.10</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>89,344</t>
+          <t>69,593</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>114/11/14</t>
+          <t>114/10/16</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>223192943</t>
+          <t>115801585</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>13,766,027,280</t>
+          <t>7,243,965,563</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>61.65</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>61.90</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.40</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>61.70</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>+1.20</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>277,389</t>
+          <t>69,793</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>114/11/17</t>
+          <t>114/10/17</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>91925734</t>
+          <t>166191884</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>5,696,893,851</t>
+          <t>10,319,476,518</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>62.00</t>
+          <t>62.05</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>62.20</t>
+          <t>62.30</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>61.90</t>
+          <t>62.05</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>+0.20</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>85,395</t>
+          <t>150,480</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>114/11/18</t>
+          <t>114/10/20</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>264956405</t>
+          <t>105854638</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>16,077,471,840</t>
+          <t>6,661,383,731</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>61.30</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>61.30</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.30</t>
+          <t>62.15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>60.45</t>
+          <t>63.10</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>+1.05</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>354,183</t>
+          <t>71,439</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>114/11/19</t>
+          <t>114/10/21</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>151383859</t>
+          <t>128793394</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9,097,742,490</t>
+          <t>8,163,510,301</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>63.40</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>60.50</t>
+          <t>63.65</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>59.90</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>60.05</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>+0.10</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>198,226</t>
+          <t>81,028</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>114/11/20</t>
+          <t>114/10/22</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>84027889</t>
+          <t>124303290</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>5,187,294,354</t>
+          <t>7,767,140,110</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>61.55</t>
+          <t>62.60</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>62.85</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.35</t>
+          <t>62.25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>61.90</t>
+          <t>62.70</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>+1.85</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>61,552</t>
+          <t>129,615</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>114/11/21</t>
+          <t>114/10/23</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>327691489</t>
+          <t>166688171</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>19,593,794,724</t>
+          <t>10,363,437,208</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>60.10</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>59.50</t>
+          <t>61.75</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>410,104</t>
+          <t>93,117</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>114/11/24</t>
+          <t>114/10/27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>162722018</t>
+          <t>104776108</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9,712,201,417</t>
+          <t>6,669,961,671</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>60.10</t>
+          <t>63.75</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>60.10</t>
+          <t>63.90</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>59.45</t>
+          <t>63.45</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>59.55</t>
+          <t>63.80</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>+1.45</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>155,513</t>
+          <t>64,536</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>114/11/25</t>
+          <t>114/10/28</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>64411018</t>
+          <t>99770041</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>3,893,075,835</t>
+          <t>6,330,563,186</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>60.70</t>
+          <t>63.55</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>60.75</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.10</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>60.35</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>+0.80</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>51,135</t>
+          <t>102,903</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>114/11/26</t>
+          <t>114/10/29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>75793554</t>
+          <t>67414369</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4,646,516,112</t>
+          <t>4,326,680,379</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>61.10</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>61.50</t>
+          <t>64.45</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.00</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>61.35</t>
+          <t>64.40</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>+1.00</t>
+          <t>+1.05</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>49,069</t>
+          <t>50,482</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>114/11/27</t>
+          <t>114/10/30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>53852335</t>
+          <t>95106510</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3,333,400,290</t>
+          <t>6,125,525,659</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>64.60</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>64.80</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.65</t>
+          <t>64.00</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>61.90</t>
+          <t>64.40</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>+0.55</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>39,232</t>
+          <t>77,635</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>114/11/28</t>
+          <t>114/10/31</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>68386478</t>
+          <t>55956524</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>4,252,497,861</t>
+          <t>3,616,991,558</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>64.60</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>64.80</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.85</t>
+          <t>64.40</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>64.75</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>+0.35</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>37,281</t>
+          <t>44,302</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>114/12/01</t>
+          <t>114/11/03</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>103003085</t>
+          <t>140157410</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>6,350,023,506</t>
+          <t>9,004,715,647</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>64.45</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>64.80</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.40</t>
+          <t>63.90</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>61.50</t>
+          <t>64.15</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>105,261</t>
+          <t>154,188</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>114/12/02</t>
+          <t>114/11/04</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>43152711</t>
+          <t>88131032</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2,670,762,886</t>
+          <t>5,658,007,897</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>64.50</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>62.20</t>
+          <t>64.85</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.65</t>
+          <t>63.85</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>61.70</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>+0.20</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>33,675</t>
+          <t>90,876</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>114/12/03</t>
+          <t>114/11/05</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>46546830</t>
+          <t>229413552</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2,900,511,764</t>
+          <t>14,391,151,897</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>62.30</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>62.30</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>+0.60</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>34,300</t>
+          <t>276,109</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>114/12/04</t>
+          <t>114/11/06</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>40655322</t>
+          <t>68680372</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2,530,843,780</t>
+          <t>4,349,732,858</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>63.50</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>62.00</t>
+          <t>63.15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>62.20</t>
+          <t>63.30</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>35,535</t>
+          <t>57,358</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>114/12/05</t>
+          <t>114/11/07</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>47277037</t>
+          <t>111187957</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2,958,378,181</t>
+          <t>6,952,850,646</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>62.45</t>
+          <t>62.65</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4686,430 +4686,430 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>62.55</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>+0.55</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>44,751</t>
+          <t>136,880</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>114/12/08</t>
+          <t>114/11/10</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>78686347</t>
+          <t>83130868</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>4,991,038,407</t>
+          <t>5,234,605,606</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>62.80</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>62.95</t>
+          <t>62.60</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>+0.95</t>
+          <t>+0.80</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>60,124</t>
+          <t>61,928</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>114/12/09</t>
+          <t>114/11/11</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>50671148</t>
+          <t>79723934</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>3,225,750,796</t>
+          <t>5,046,877,473</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>63.80</t>
+          <t>63.65</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>63.85</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>63.55</t>
+          <t>62.85</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>63.60</t>
+          <t>62.90</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>49,273</t>
+          <t>85,077</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>114/12/10</t>
+          <t>114/11/12</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>66717948</t>
+          <t>62620173</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>4,264,783,464</t>
+          <t>3,947,348,693</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>63.30</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>63.65</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>64.05</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>+0.30</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>51,254</t>
+          <t>55,267</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>114/12/11</t>
+          <t>114/11/13</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>101197570</t>
+          <t>80483242</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>6,442,627,838</t>
+          <t>5,053,859,324</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>64.30</t>
+          <t>62.80</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>64.50</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>62.60</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>63.35</t>
+          <t>62.90</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>110,925</t>
+          <t>89,344</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>114/12/12</t>
+          <t>114/11/14</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>60240146</t>
+          <t>223192943</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>3,825,611,936</t>
+          <t>13,766,027,280</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>63.55</t>
+          <t>61.65</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>63.80</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>63.30</t>
+          <t>61.40</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>63.45</t>
+          <t>61.70</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>+0.10</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>49,189</t>
+          <t>277,389</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>114/12/15</t>
+          <t>114/11/17</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>114939409</t>
+          <t>91925734</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>7,203,513,013</t>
+          <t>5,696,893,851</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>62.00</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>62.85</t>
+          <t>62.20</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>62.80</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>+0.20</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>134,546</t>
+          <t>85,395</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>114/12/16</t>
+          <t>114/11/18</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>169375708</t>
+          <t>264956405</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>10,494,294,870</t>
+          <t>16,077,471,840</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>61.30</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>62.25</t>
+          <t>61.30</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.70</t>
+          <t>60.30</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>62.25</t>
+          <t>60.45</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>211,332</t>
+          <t>354,183</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>114/12/17</t>
+          <t>114/11/19</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>98504980</t>
+          <t>151383859</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>6,122,747,371</t>
+          <t>9,097,742,490</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>62.15</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>62.45</t>
+          <t>60.50</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.85</t>
+          <t>59.90</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>61.90</t>
+          <t>60.05</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>86,356</t>
+          <t>198,226</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>114/12/18</t>
+          <t>114/11/20</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>117973409</t>
+          <t>84027889</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>7,287,940,742</t>
+          <t>5,187,294,354</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>61.80</t>
+          <t>61.55</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>62.10</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.55</t>
+          <t>61.35</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5119,237 +5119,237 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+1.85</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>87,078</t>
+          <t>61,552</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>114/12/19</t>
+          <t>114/11/21</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>81027467</t>
+          <t>327691489</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>5,067,295,440</t>
+          <t>19,593,794,724</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>62.40</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>62.35</t>
+          <t>59.50</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>59.85</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>+0.60</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>41,675</t>
+          <t>410,104</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>114/12/22</t>
+          <t>114/11/24</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>93882538</t>
+          <t>162722018</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>5,942,586,403</t>
+          <t>9,712,201,417</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>63.30</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>63.45</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>63.05</t>
+          <t>59.45</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>63.40</t>
+          <t>59.55</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>+0.90</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>52,777</t>
+          <t>155,513</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>114/12/23</t>
+          <t>114/11/25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>101867829</t>
+          <t>64411018</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>6,483,053,926</t>
+          <t>3,893,075,835</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>63.50</t>
+          <t>60.70</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>63.80</t>
+          <t>60.75</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>63.50</t>
+          <t>60.10</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>63.70</t>
+          <t>60.35</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>+0.30</t>
+          <t>+0.80</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>44,429</t>
+          <t>51,135</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>114/12/24</t>
+          <t>114/11/26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>64106420</t>
+          <t>75793554</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4,094,914,827</t>
+          <t>4,646,516,112</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>61.10</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>64.05</t>
+          <t>61.50</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>63.75</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>63.85</t>
+          <t>61.35</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>+1.00</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>41,909</t>
+          <t>49,069</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>114/12/26</t>
+          <t>114/11/27</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>70816194</t>
+          <t>53852335</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4,556,213,637</t>
+          <t>3,333,400,290</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>64.20</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>64.50</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>64.10</t>
+          <t>61.65</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>64.40</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5359,4846 +5359,5786 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>54,305</t>
+          <t>39,232</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>114/12/29</t>
+          <t>114/11/28</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>86510015</t>
+          <t>68386478</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>5,628,464,300</t>
+          <t>4,252,497,861</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>64.65</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>65.35</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>64.60</t>
+          <t>61.85</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>65.25</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>+0.85</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>63,528</t>
+          <t>37,281</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>114/12/30</t>
+          <t>114/12/01</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>61058197</t>
+          <t>103003085</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3,970,585,296</t>
+          <t>6,350,023,506</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>64.90</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>65.30</t>
+          <t>61.95</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>64.75</t>
+          <t>61.40</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>61.50</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>54,458</t>
+          <t>105,261</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>114/12/31</t>
+          <t>114/12/02</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>71868485</t>
+          <t>43152711</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>4,709,518,474</t>
+          <t>2,670,762,886</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>65.10</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>62.20</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>64.90</t>
+          <t>61.65</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>65.60</t>
+          <t>61.70</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>+0.20</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>52,512</t>
+          <t>33,675</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>115/01/02</t>
+          <t>114/12/03</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>81135717</t>
+          <t>46546830</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>5,396,295,605</t>
+          <t>2,900,511,764</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>66.00</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>67.00</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>65.80</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>62.30</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>+1.35</t>
+          <t>+0.60</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>69,896</t>
+          <t>34,300</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>115/01/05</t>
+          <t>114/12/04</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>232910010</t>
+          <t>40655322</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>16,163,783,922</t>
+          <t>2,530,843,780</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>68.10</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>68.05</t>
+          <t>62.00</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>69.50</t>
+          <t>62.20</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>+2.55</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>141,745</t>
+          <t>35,535</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>115/01/06</t>
+          <t>114/12/05</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>130176548</t>
+          <t>47277037</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>9,090,693,014</t>
+          <t>2,958,378,181</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>69.45</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>70.40</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>68.95</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>70.40</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>+0.90</t>
+          <t>+0.55</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>94,772</t>
+          <t>44,751</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>115/01/07</t>
+          <t>114/12/08</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>122267721</t>
+          <t>78686347</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>8,554,349,889</t>
+          <t>4,991,038,407</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>70.40</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.70</t>
+          <t>62.95</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>+0.95</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>132,657</t>
+          <t>60,124</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>115/01/08</t>
+          <t>114/12/09</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>74866080</t>
+          <t>50671148</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>5,233,314,685</t>
+          <t>3,225,750,796</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>69.65</t>
+          <t>63.80</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>63.85</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.40</t>
+          <t>63.55</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>70.10</t>
+          <t>63.60</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>+0.25</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>65,275</t>
+          <t>49,273</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>115/01/09</t>
+          <t>114/12/10</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>113278257</t>
+          <t>66717948</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>7,882,596,065</t>
+          <t>4,264,783,464</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>69.80</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>68.90</t>
+          <t>63.65</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>64.05</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>117,481</t>
+          <t>51,254</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>115/01/12</t>
+          <t>114/12/11</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>84346348</t>
+          <t>101197570</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>5,928,941,344</t>
+          <t>6,442,627,838</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>70.50</t>
+          <t>64.30</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>70.55</t>
+          <t>64.50</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>70.35</t>
+          <t>63.35</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>+0.50</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>74,258</t>
+          <t>110,925</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>115/01/13</t>
+          <t>114/12/12</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>103565147</t>
+          <t>60240146</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>7,323,170,787</t>
+          <t>3,825,611,936</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>71.10</t>
+          <t>63.55</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>71.20</t>
+          <t>63.80</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>70.30</t>
+          <t>63.30</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>70.70</t>
+          <t>63.45</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>+0.35</t>
+          <t>+0.10</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>77,504</t>
+          <t>49,189</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>115/01/14</t>
+          <t>114/12/15</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>86322515</t>
+          <t>114939409</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>6,115,431,229</t>
+          <t>7,203,513,013</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>70.95</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>71.10</t>
+          <t>62.85</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>70.65</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>70.75</t>
+          <t>62.80</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>+0.05</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>67,445</t>
+          <t>134,546</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>115/01/15</t>
+          <t>114/12/16</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>97455363</t>
+          <t>169375708</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>6,856,607,422</t>
+          <t>10,494,294,870</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>70.70</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>70.70</t>
+          <t>62.25</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>61.70</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>70.65</t>
+          <t>62.25</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>122,171</t>
+          <t>211,332</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>115/01/16</t>
+          <t>114/12/17</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>101069992</t>
+          <t>98504980</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>7,242,693,243</t>
+          <t>6,122,747,371</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>62.15</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>72.10</t>
+          <t>62.45</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>71.20</t>
+          <t>61.85</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>+1.35</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>80,151</t>
+          <t>86,356</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>115/01/19</t>
+          <t>114/12/18</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>122970595</t>
+          <t>117973409</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>8,839,245,132</t>
+          <t>7,287,940,742</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>61.80</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>72.80</t>
+          <t>62.10</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>61.55</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>72.60</t>
+          <t>61.90</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>+0.60</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>107,729</t>
+          <t>87,078</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>115/01/20</t>
+          <t>114/12/19</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>111046335</t>
+          <t>81027467</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>8,024,448,821</t>
+          <t>5,067,295,440</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>71.90</t>
+          <t>62.40</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>72.65</t>
+          <t>62.75</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>72.60</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+0.60</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>99,563</t>
+          <t>41,675</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>115/01/21</t>
+          <t>114/12/22</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>173683092</t>
+          <t>93882538</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>12,502,883,011</t>
+          <t>5,942,586,403</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>71.80</t>
+          <t>63.30</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>72.50</t>
+          <t>63.45</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>63.05</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>63.40</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>+0.90</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>203,410</t>
+          <t>52,777</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>115/01/22</t>
+          <t>114/12/23</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>101703005</t>
+          <t>101867829</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>7,306,066,892</t>
+          <t>6,483,053,926</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>71.90</t>
+          <t>63.50</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>72.05</t>
+          <t>63.80</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>71.60</t>
+          <t>63.50</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>71.80</t>
+          <t>63.70</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>X0.00</t>
+          <t>+0.30</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>92,128</t>
+          <t>44,429</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>115/01/23</t>
+          <t>114/12/24</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>70983017</t>
+          <t>64106420</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>5,116,365,718</t>
+          <t>4,094,914,827</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>72.10</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>72.30</t>
+          <t>64.05</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>71.80</t>
+          <t>63.75</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>63.85</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>+0.45</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>49,675</t>
+          <t>41,909</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>115/01/26</t>
+          <t>114/12/26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>87992466</t>
+          <t>70816194</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>6,373,835,828</t>
+          <t>4,556,213,637</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>64.20</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>72.65</t>
+          <t>64.50</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>72.20</t>
+          <t>64.10</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>64.40</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+0.55</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>72,487</t>
+          <t>54,305</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>115/01/27</t>
+          <t>114/12/29</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>73059634</t>
+          <t>86510015</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>5,322,600,617</t>
+          <t>5,628,464,300</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>72.40</t>
+          <t>64.65</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>65.35</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>64.60</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>65.25</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>+0.80</t>
+          <t>+0.85</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>53,680</t>
+          <t>63,528</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>115/01/28</t>
+          <t>114/12/30</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>90901846</t>
+          <t>61058197</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>6,711,076,738</t>
+          <t>3,970,585,296</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>73.55</t>
+          <t>64.90</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>74.20</t>
+          <t>65.30</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>73.50</t>
+          <t>64.75</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>74.20</t>
+          <t>65.15</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>+1.15</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>67,825</t>
+          <t>54,458</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>115/01/29</t>
+          <t>114/12/31</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>119914950</t>
+          <t>71868485</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>8,867,286,368</t>
+          <t>4,709,518,474</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>74.40</t>
+          <t>65.10</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>74.50</t>
+          <t>65.85</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>73.50</t>
+          <t>64.90</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>65.60</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>121,772</t>
+          <t>52,512</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>115/01/30</t>
+          <t>115/01/02</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>175275799</t>
+          <t>81135717</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>12,738,811,404</t>
+          <t>5,396,295,605</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>66.00</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>73.20</t>
+          <t>67.00</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>72.30</t>
+          <t>65.80</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>72.60</t>
+          <t>66.95</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>+1.35</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>241,546</t>
+          <t>69,896</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>115/02/02</t>
+          <t>115/01/05</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>234325396</t>
+          <t>232910010</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>16,687,566,456</t>
+          <t>16,163,783,922</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>71.55</t>
+          <t>68.10</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>70.90</t>
+          <t>68.05</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>71.50</t>
+          <t>69.50</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>+2.55</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>332,048</t>
+          <t>141,745</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>115/02/03</t>
+          <t>115/01/06</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>73734001</t>
+          <t>130176548</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>5,367,935,502</t>
+          <t>9,090,693,014</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>73.00</t>
+          <t>69.45</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>70.40</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>72.40</t>
+          <t>68.95</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>72.95</t>
+          <t>70.40</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>+1.45</t>
+          <t>+0.90</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>60,314</t>
+          <t>94,772</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>115/02/04</t>
+          <t>115/01/07</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>59733704</t>
+          <t>122267721</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>4,346,370,749</t>
+          <t>8,554,349,889</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>72.40</t>
+          <t>70.40</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>72.30</t>
+          <t>69.70</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>72.90</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>55,518</t>
+          <t>132,657</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>115/02/05</t>
+          <t>115/01/08</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>107575796</t>
+          <t>74866080</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>7,742,810,789</t>
+          <t>5,233,314,685</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>72.05</t>
+          <t>69.65</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>70.35</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>69.40</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>72.00</t>
+          <t>70.10</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>+0.25</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>175,926</t>
+          <t>65,275</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>115/02/06</t>
+          <t>115/01/09</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>110883112</t>
+          <t>113278257</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>7,920,520,483</t>
+          <t>7,882,596,065</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>71.40</t>
+          <t>69.80</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>72.25</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>70.80</t>
+          <t>68.90</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>71.90</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>134,413</t>
+          <t>117,481</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>115/02/09</t>
+          <t>115/01/12</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>122340661</t>
+          <t>84346348</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>9,050,873,718</t>
+          <t>5,928,941,344</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>74.05</t>
+          <t>70.50</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>74.15</t>
+          <t>70.55</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>70.35</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>+2.05</t>
+          <t>+0.50</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>81,342</t>
+          <t>74,258</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>115/02/10</t>
+          <t>115/01/13</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>102315945</t>
+          <t>103565147</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>7,703,131,124</t>
+          <t>7,323,170,787</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>74.65</t>
+          <t>71.10</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>71.20</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>74.60</t>
+          <t>70.30</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>70.70</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>+1.55</t>
+          <t>+0.35</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>80,773</t>
+          <t>77,504</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>115/02/11</t>
+          <t>115/01/14</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>120639150</t>
+          <t>86322515</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>9,275,271,308</t>
+          <t>6,115,431,229</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>70.95</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>77.45</t>
+          <t>71.10</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>70.65</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>77.20</t>
+          <t>70.75</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>+1.70</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>118,568</t>
+          <t>67,445</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>115/02/23</t>
+          <t>115/01/15</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>227936939</t>
+          <t>97455363</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>17,749,552,954</t>
+          <t>6,856,607,422</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>70.70</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>70.70</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>77.20</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>77.40</t>
+          <t>70.65</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>+0.20</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>220,396</t>
+          <t>122,171</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>115/02/24</t>
+          <t>115/01/16</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>150367766</t>
+          <t>101069992</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>11,848,589,798</t>
+          <t>7,242,693,243</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>77.95</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>79.65</t>
+          <t>72.10</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>77.85</t>
+          <t>71.20</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>79.40</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>+2.00</t>
+          <t>+1.35</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>117,830</t>
+          <t>80,151</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>115/02/25</t>
+          <t>115/01/19</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>167423484</t>
+          <t>122970595</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>13,565,896,459</t>
+          <t>8,839,245,132</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>81.80</t>
+          <t>72.80</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>71.45</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>81.10</t>
+          <t>72.60</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>+1.70</t>
+          <t>+0.60</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>141,615</t>
+          <t>107,729</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>115/02/26</t>
+          <t>115/01/20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>133517321</t>
+          <t>111046335</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>10,841,079,880</t>
+          <t>8,024,448,821</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>81.25</t>
+          <t>71.90</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>81.50</t>
+          <t>72.65</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>80.80</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>81.15</t>
+          <t>72.60</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>+0.05</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>133,768</t>
+          <t>99,563</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>115/03/02</t>
+          <t>115/01/21</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>224651381</t>
+          <t>173683092</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>18,053,460,439</t>
+          <t>12,502,883,011</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>79.50</t>
+          <t>71.80</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>80.80</t>
+          <t>72.50</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>79.15</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>80.35</t>
+          <t>71.85</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>297,372</t>
+          <t>203,410</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>115/03/03</t>
+          <t>115/01/22</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>324317518</t>
+          <t>101703005</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>25,713,110,082</t>
+          <t>7,306,066,892</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>80.05</t>
+          <t>71.90</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>80.40</t>
+          <t>72.05</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>78.65</t>
+          <t>71.60</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>78.75</t>
+          <t>71.80</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>X0.00</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>516,152</t>
+          <t>92,128</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>115/03/04</t>
+          <t>115/01/23</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>505217770</t>
+          <t>70983017</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>38,471,650,068</t>
+          <t>5,116,365,718</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>77.40</t>
+          <t>72.10</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>77.45</t>
+          <t>72.30</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>71.80</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>+0.45</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>711,329</t>
+          <t>49,675</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>115/03/05</t>
+          <t>115/01/26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>207004644</t>
+          <t>87992466</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>16,090,040,992</t>
+          <t>6,373,835,828</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>78.30</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>78.85</t>
+          <t>72.65</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>76.70</t>
+          <t>72.20</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>77.40</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>+1.80</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>204,272</t>
+          <t>72,487</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>115/03/06</t>
+          <t>115/01/27</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>151611764</t>
+          <t>73059634</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>11,638,160,681</t>
+          <t>5,322,600,617</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>76.80</t>
+          <t>72.40</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>77.30</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>72.35</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>76.85</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>+0.80</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>179,651</t>
+          <t>53,680</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>115/03/09</t>
+          <t>115/01/28</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>542230074</t>
+          <t>90901846</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>39,488,306,757</t>
+          <t>6,711,076,738</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>73.15</t>
+          <t>73.55</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>73.60</t>
+          <t>74.20</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>71.65</t>
+          <t>73.50</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>73.60</t>
+          <t>74.20</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>+1.15</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>658,991</t>
+          <t>67,825</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>115/03/10</t>
+          <t>115/01/29</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>173870150</t>
+          <t>119914950</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>13,134,447,601</t>
+          <t>8,867,286,368</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>74.40</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>74.50</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>74.30</t>
+          <t>73.50</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>75.20</t>
+          <t>73.75</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>+1.60</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>180,826</t>
+          <t>121,772</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>115/03/11</t>
+          <t>115/01/30</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>151798656</t>
+          <t>175275799</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>11,785,499,671</t>
+          <t>12,738,811,404</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>78.50</t>
+          <t>73.20</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>76.10</t>
+          <t>72.30</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>78.20</t>
+          <t>72.60</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>+3.00</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>104,693</t>
+          <t>241,546</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>115/03/12</t>
+          <t>115/02/02</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>131518817</t>
+          <t>234325396</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>10,107,953,882</t>
+          <t>16,687,566,456</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>77.10</t>
+          <t>71.55</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>77.60</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>76.35</t>
+          <t>70.90</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>76.60</t>
+          <t>71.50</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>180,533</t>
+          <t>332,048</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>115/03/13</t>
+          <t>115/02/03</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>115111624</t>
+          <t>73734001</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>8,723,084,020</t>
+          <t>5,367,935,502</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>75.15</t>
+          <t>73.00</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>76.55</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>72.40</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>75.95</t>
+          <t>72.95</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>+1.45</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>160,164</t>
+          <t>60,314</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>115/03/16</t>
+          <t>115/02/04</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>105392137</t>
+          <t>59733704</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>7,994,232,270</t>
+          <t>4,346,370,749</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>72.40</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>76.70</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>75.45</t>
+          <t>72.30</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>72.90</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>135,317</t>
+          <t>55,518</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>115/03/17</t>
+          <t>115/02/05</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>63986997</t>
+          <t>107575796</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>4,901,077,314</t>
+          <t>7,742,810,789</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>72.05</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>77.00</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>71.75</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>76.65</t>
+          <t>72.00</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>+1.05</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>54,634</t>
+          <t>175,926</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>115/03/18</t>
+          <t>115/02/06</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>78000193</t>
+          <t>110883112</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>6,064,253,100</t>
+          <t>7,920,520,483</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>77.75</t>
+          <t>71.40</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>78.05</t>
+          <t>72.25</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>77.45</t>
+          <t>70.80</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>77.80</t>
+          <t>71.90</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>+1.15</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>65,062</t>
+          <t>134,413</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>115/03/19</t>
+          <t>115/02/09</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>141733755</t>
+          <t>122340661</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>10,821,638,440</t>
+          <t>9,050,873,718</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>76.60</t>
+          <t>74.05</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>76.80</t>
+          <t>74.15</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>75.95</t>
+          <t>73.75</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>76.00</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>+2.05</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>218,952</t>
+          <t>81,342</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>115/03/20</t>
+          <t>115/02/10</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>72638922</t>
+          <t>102315945</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>5,517,624,557</t>
+          <t>7,703,131,124</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>76.20</t>
+          <t>74.65</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>76.40</t>
+          <t>75.50</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
+          <t>74.60</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
           <t>75.50</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>75.90</t>
-        </is>
-      </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+1.55</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>101,109</t>
+          <t>80,773</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>115/03/23</t>
+          <t>115/02/11</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>233385121</t>
+          <t>120639150</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>17,256,278,289</t>
+          <t>9,275,271,308</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>73.50</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>74.45</t>
+          <t>77.45</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>73.30</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>77.20</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>+1.70</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>340,169</t>
+          <t>118,568</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>115/03/24</t>
+          <t>115/02/23</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>90466270</t>
+          <t>227936939</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>6,750,345,110</t>
+          <t>17,749,552,954</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>75.50</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>78.45</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>73.80</t>
+          <t>77.20</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>74.40</t>
+          <t>77.40</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>+0.20</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>111,636</t>
+          <t>220,396</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>115/03/25</t>
+          <t>115/02/24</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>94344080</t>
+          <t>150367766</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>7,201,277,589</t>
+          <t>11,848,589,798</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>76.35</t>
+          <t>77.95</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>76.65</t>
+          <t>79.65</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>76.00</t>
+          <t>77.85</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>76.20</t>
+          <t>79.40</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>+1.80</t>
+          <t>+2.00</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>66,655</t>
+          <t>117,830</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>115/03/26</t>
+          <t>115/02/25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>80069071</t>
+          <t>167423484</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>6,102,674,371</t>
+          <t>13,565,896,459</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>76.30</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>76.85</t>
+          <t>81.80</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>75.60</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>75.80</t>
+          <t>81.10</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>+1.70</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>80,270</t>
+          <t>141,615</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>115/03/27</t>
+          <t>115/02/26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>115798710</t>
+          <t>133517321</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>8,622,872,378</t>
+          <t>10,841,079,880</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>74.45</t>
+          <t>81.25</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>75.10</t>
+          <t>81.50</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>74.10</t>
+          <t>80.80</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>81.15</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>161,501</t>
+          <t>133,768</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>115/03/30</t>
+          <t>115/03/02</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>175515568</t>
+          <t>224651381</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>12,905,676,995</t>
+          <t>18,053,460,439</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>73.30</t>
+          <t>79.50</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>74.05</t>
+          <t>80.80</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>72.80</t>
+          <t>79.15</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>73.90</t>
+          <t>80.35</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>261,697</t>
+          <t>297,372</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>115/03/31</t>
+          <t>115/03/03</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>257738774</t>
+          <t>324317518</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>18,741,416,482</t>
+          <t>25,713,110,082</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>73.35</t>
+          <t>80.05</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>73.45</t>
+          <t>80.40</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>72.15</t>
+          <t>78.65</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>78.75</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>400,630</t>
+          <t>516,152</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>115/04/01</t>
+          <t>115/03/04</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>130698663</t>
+          <t>505217770</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>9,824,716,760</t>
+          <t>38,471,650,068</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>77.40</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
+          <t>77.45</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>75.50</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
           <t>75.60</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>74.60</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>75.45</t>
-        </is>
-      </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>+3.10</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>89,221</t>
+          <t>711,329</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>115/04/02</t>
+          <t>115/03/05</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>113976137</t>
+          <t>207004644</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>8,478,357,215</t>
+          <t>16,090,040,992</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>75.90</t>
+          <t>78.30</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>78.85</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>73.80</t>
+          <t>76.70</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>77.40</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>+1.80</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>162,558</t>
+          <t>204,272</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>115/04/07</t>
+          <t>115/03/06</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>80449813</t>
+          <t>151611764</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>6,046,717,969</t>
+          <t>11,638,160,681</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>75.15</t>
+          <t>76.80</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>75.45</t>
+          <t>77.30</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>74.65</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>75.30</t>
+          <t>76.85</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>+1.35</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>81,117</t>
+          <t>179,651</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>115/04/08</t>
+          <t>115/03/09</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>235675856</t>
+          <t>542230074</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>18,578,257,980</t>
+          <t>39,488,306,757</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>78.10</t>
+          <t>73.15</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>79.25</t>
+          <t>73.60</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>78.10</t>
+          <t>71.65</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>79.20</t>
+          <t>73.60</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>+3.90</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>148,473</t>
+          <t>658,991</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>115/04/09</t>
+          <t>115/03/10</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>95094893</t>
+          <t>173870150</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>7,520,522,079</t>
+          <t>13,134,447,601</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>79.30</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>79.40</t>
+          <t>76.25</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>78.80</t>
+          <t>74.30</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>79.15</t>
+          <t>75.20</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>+1.60</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>72,839</t>
+          <t>180,826</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>115/04/10</t>
+          <t>115/03/11</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>120838644</t>
+          <t>151798656</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>9,724,171,699</t>
+          <t>11,785,499,671</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>80.80</t>
+          <t>78.50</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>79.95</t>
+          <t>76.10</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>80.75</t>
+          <t>78.20</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>+1.60</t>
+          <t>+3.00</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>98,770</t>
+          <t>104,693</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>115/04/13</t>
+          <t>115/03/12</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>91689847</t>
+          <t>131518817</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>7,398,471,916</t>
+          <t>10,107,953,882</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>80.60</t>
+          <t>77.10</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>81.00</t>
+          <t>77.60</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>80.40</t>
+          <t>76.35</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>80.60</t>
+          <t>76.60</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>86,103</t>
+          <t>180,533</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>115/04/14</t>
+          <t>115/03/13</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>129128623</t>
+          <t>115111624</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>10,668,730,259</t>
+          <t>8,723,084,020</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>81.75</t>
+          <t>75.15</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>83.20</t>
+          <t>76.55</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>81.75</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>83.10</t>
+          <t>75.95</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>+2.50</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>101,069</t>
+          <t>160,164</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>115/04/15</t>
+          <t>115/03/16</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>127729350</t>
+          <t>105392137</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>10,793,181,456</t>
+          <t>7,994,232,270</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>84.10</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>85.10</t>
+          <t>76.70</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>83.80</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>+1.05</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>122,459</t>
+          <t>135,317</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>115/04/16</t>
+          <t>115/03/17</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>80696269</t>
+          <t>63986997</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>6,829,488,057</t>
+          <t>4,901,077,314</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>84.75</t>
+          <t>76.45</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>85.10</t>
+          <t>77.00</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>76.65</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>+0.85</t>
+          <t>+1.05</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>78,794</t>
+          <t>54,634</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>115/04/17</t>
+          <t>115/03/18</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>101258031</t>
+          <t>78000193</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>8,526,065,307</t>
+          <t>6,064,253,100</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>84.20</t>
+          <t>77.75</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>84.50</t>
+          <t>78.05</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>84.00</t>
+          <t>77.45</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>77.80</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>+1.15</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>146,785</t>
+          <t>65,062</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>115/04/20</t>
+          <t>115/03/19</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>100551500</t>
+          <t>141733755</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>8,533,691,370</t>
+          <t>10,821,638,440</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>84.55</t>
+          <t>76.60</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>85.10</t>
+          <t>76.80</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>84.45</t>
+          <t>75.95</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>84.55</t>
+          <t>76.00</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>+0.40</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>90,566</t>
+          <t>218,952</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>115/04/21</t>
+          <t>115/03/20</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>75557759</t>
+          <t>72638922</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>6,477,242,890</t>
+          <t>5,517,624,557</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>85.50</t>
+          <t>76.20</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>86.10</t>
+          <t>76.40</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>75.50</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>86.00</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>+1.45</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>72,495</t>
+          <t>101,109</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>115/04/22</t>
+          <t>115/03/23</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>67544248</t>
+          <t>233385121</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>5,828,004,375</t>
+          <t>17,256,278,289</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>85.75</t>
+          <t>73.50</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>86.60</t>
+          <t>74.45</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>85.55</t>
+          <t>73.30</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>86.35</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>+0.35</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>70,385</t>
+          <t>340,169</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>115/04/23</t>
+          <t>115/03/24</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>156715780</t>
+          <t>90466270</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>13,599,617,688</t>
+          <t>6,750,345,110</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>87.65</t>
+          <t>75.50</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>88.80</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>73.80</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>86.35</t>
+          <t>74.40</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>161,030</t>
+          <t>111,636</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>115/04/24</t>
+          <t>115/03/25</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>129885911</t>
+          <t>94344080</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>11,539,759,376</t>
+          <t>7,201,277,589</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>87.60</t>
+          <t>76.35</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>76.65</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>87.55</t>
+          <t>76.00</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>76.20</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>+3.60</t>
+          <t>+1.80</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>99,531</t>
+          <t>66,655</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>115/04/27</t>
+          <t>115/03/26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>192038103</t>
+          <t>80069071</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>17,927,615,310</t>
+          <t>6,102,674,371</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>92.70</t>
+          <t>76.30</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>94.25</t>
+          <t>76.85</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>92.70</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>93.00</t>
+          <t>75.80</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>+3.05</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>172,215</t>
+          <t>80,270</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>115/04/28</t>
+          <t>115/03/27</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>126301332</t>
+          <t>115798710</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>11,691,553,456</t>
+          <t>8,622,872,378</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>92.55</t>
+          <t>74.45</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>93.65</t>
+          <t>75.10</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>91.90</t>
+          <t>74.10</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>92.00</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>193,633</t>
+          <t>161,501</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>115/04/29</t>
+          <t>115/03/30</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>103795530</t>
+          <t>175515568</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>9,410,136,420</t>
+          <t>12,905,676,995</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>90.70</t>
+          <t>73.30</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>91.50</t>
+          <t>74.05</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>90.00</t>
+          <t>72.80</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>90.75</t>
+          <t>73.90</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>163,856</t>
+          <t>261,697</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>115/04/30</t>
+          <t>115/03/31</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>89209769</t>
+          <t>257738774</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>8,111,730,781</t>
+          <t>18,741,416,482</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>91.25</t>
+          <t>73.35</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>91.90</t>
+          <t>73.45</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>90.30</t>
+          <t>72.15</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>90.50</t>
+          <t>72.35</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>125,264</t>
+          <t>400,630</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>115/05/04</t>
+          <t>115/04/01</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>125270935</t>
+          <t>130698663</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>11,748,311,547</t>
+          <t>9,824,716,760</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>92.50</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>94.65</t>
+          <t>75.60</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>92.40</t>
+          <t>74.60</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>94.60</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>+4.10</t>
+          <t>+3.10</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>114,510</t>
+          <t>89,221</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>115/05/05</t>
+          <t>115/04/02</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>82851869</t>
+          <t>113976137</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>7,821,971,023</t>
+          <t>8,478,357,215</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>94.40</t>
+          <t>75.90</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>94.75</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>94.00</t>
+          <t>73.80</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>94.60</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 0.00</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>115,951</t>
+          <t>162,558</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>115/05/06</t>
+          <t>115/04/07</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>111759164</t>
+          <t>80449813</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>10,703,702,958</t>
+          <t>6,046,717,969</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>96.05</t>
+          <t>75.15</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>96.90</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>94.70</t>
+          <t>74.65</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>95.75</t>
+          <t>75.30</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>+1.15</t>
+          <t>+1.35</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>120,555</t>
+          <t>81,117</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>115/05/07</t>
+          <t>115/04/08</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>117152238</t>
+          <t>235675856</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>11,472,448,704</t>
+          <t>18,578,257,980</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>97.95</t>
+          <t>78.10</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>98.40</t>
+          <t>79.25</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>97.40</t>
+          <t>78.10</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>97.70</t>
+          <t>79.20</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>+1.95</t>
+          <t>+3.90</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>119,685</t>
+          <t>148,473</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>115/05/08</t>
+          <t>115/04/09</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>131188123</t>
+          <t>95094893</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>12,716,275,565</t>
+          <t>7,520,522,079</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>97.35</t>
+          <t>79.30</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>97.70</t>
+          <t>79.40</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>95.85</t>
+          <t>78.80</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>97.00</t>
+          <t>79.15</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>217,822</t>
+          <t>72,839</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>115/05/11</t>
+          <t>115/04/10</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>96606391</t>
+          <t>120838644</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>9,362,479,353</t>
+          <t>9,724,171,699</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>96.65</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>97.15</t>
+          <t>80.80</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>96.50</t>
+          <t>79.95</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>96.90</t>
+          <t>80.75</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>+1.60</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>148,902</t>
+          <t>98,770</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>115/05/12</t>
+          <t>115/04/13</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>102303450</t>
+          <t>91689847</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>9,876,959,425</t>
+          <t>7,398,471,916</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>96.85</t>
+          <t>80.60</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>97.35</t>
+          <t>81.00</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>95.50</t>
+          <t>80.40</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>96.85</t>
+          <t>80.60</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>142,949</t>
+          <t>86,103</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>115/05/13</t>
+          <t>115/04/14</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>130654061</t>
+          <t>129128623</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>12,419,149,243</t>
+          <t>10,668,730,259</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>94.85</t>
+          <t>81.75</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>95.80</t>
+          <t>83.20</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>94.70</t>
+          <t>81.75</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>95.50</t>
+          <t>83.10</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>+2.50</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>260,692</t>
+          <t>101,069</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>115/05/14</t>
+          <t>115/04/15</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>57229209</t>
+          <t>127729350</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>5,510,647,058</t>
+          <t>10,793,181,456</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>96.90</t>
+          <t>84.10</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>97.20</t>
+          <t>85.10</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>95.75</t>
+          <t>83.80</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>96.05</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>+0.55</t>
+          <t>+1.05</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>70,419</t>
+          <t>122,459</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>115/05/15</t>
+          <t>115/04/16</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>98132989</t>
+          <t>80696269</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>9,472,541,597</t>
+          <t>6,829,488,057</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>97.65</t>
+          <t>84.75</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>98.25</t>
+          <t>85.10</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>95.20</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>95.40</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>+0.85</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>144,425</t>
+          <t>78,794</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>115/05/18</t>
+          <t>115/04/17</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>118571453</t>
+          <t>101258031</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>11,160,721,206</t>
+          <t>8,526,065,307</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>94.00</t>
+          <t>84.20</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>95.20</t>
+          <t>84.50</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>93.30</t>
+          <t>84.00</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>94.90</t>
+          <t>84.15</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>219,202</t>
+          <t>146,785</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>115/05/19</t>
+          <t>115/04/20</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>135939820</t>
+          <t>100551500</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>12,740,872,880</t>
+          <t>8,533,691,370</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>94.35</t>
+          <t>84.55</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>94.70</t>
+          <t>85.10</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>93.10</t>
+          <t>84.45</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>93.10</t>
+          <t>84.55</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>+0.40</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>304,750</t>
+          <t>90,566</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>115/05/20</t>
+          <t>115/04/21</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>121650308</t>
+          <t>75557759</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>11,289,688,382</t>
+          <t>6,477,242,890</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>93.00</t>
+          <t>85.50</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>93.50</t>
+          <t>86.10</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>92.45</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>92.50</t>
+          <t>86.00</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>+1.45</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>227,369</t>
+          <t>72,495</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>115/05/21</t>
+          <t>115/04/22</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>62215954</t>
+          <t>67544248</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>5,942,503,747</t>
+          <t>5,828,004,375</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>94.80</t>
+          <t>85.75</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>96.05</t>
+          <t>86.60</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>94.70</t>
+          <t>85.55</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>95.85</t>
+          <t>86.35</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>+3.35</t>
+          <t>+0.35</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>64,187</t>
+          <t>70,385</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>115/05/22</t>
+          <t>115/04/23</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>64288280</t>
+          <t>156715780</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>6,213,742,970</t>
+          <t>13,599,617,688</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>96.30</t>
+          <t>87.65</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>97.30</t>
+          <t>88.80</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>96.00</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>97.30</t>
+          <t>86.35</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>+1.45</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>70,101</t>
+          <t>161,030</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>115/05/25</t>
+          <t>115/04/24</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>129483256</t>
+          <t>129885911</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>13,010,032,076</t>
+          <t>11,539,759,376</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>99.55</t>
+          <t>87.60</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>101.00</t>
+          <t>89.95</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>99.55</t>
+          <t>87.55</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>100.80</t>
+          <t>89.95</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>+3.50</t>
+          <t>+3.60</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>107,787</t>
+          <t>99,531</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>115/05/26</t>
+          <t>115/04/27</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>93560313</t>
+          <t>192038103</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>9,432,115,613</t>
+          <t>17,927,615,310</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>101.60</t>
+          <t>92.70</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>101.80</t>
+          <t>94.25</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>100.10</t>
+          <t>92.70</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>100.10</t>
+          <t>93.00</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>+3.05</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>112,958</t>
+          <t>172,215</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>115/05/27</t>
+          <t>115/04/28</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>94959812</t>
+          <t>126301332</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>9,787,482,181</t>
+          <t>11,691,553,456</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>102.40</t>
+          <t>92.55</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>103.90</t>
+          <t>93.65</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>102.00</t>
+          <t>91.90</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>102.55</t>
+          <t>92.00</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>+2.45</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>98,413</t>
+          <t>193,633</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>115/05/28</t>
+          <t>115/04/29</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>152915695</t>
+          <t>103795530</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>15,600,509,184</t>
+          <t>9,410,136,420</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>104.00</t>
+          <t>90.70</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>104.25</t>
+          <t>91.50</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>100.10</t>
+          <t>90.00</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>100.50</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>207,536</t>
+          <t>163,856</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>115/05/29</t>
+          <t>115/04/30</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>102355526</t>
+          <t>89209769</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>10,636,250,508</t>
+          <t>8,111,730,781</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>103.20</t>
+          <t>91.25</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>105.40</t>
+          <t>91.90</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>102.70</t>
+          <t>90.30</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>105.40</t>
+          <t>90.50</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>+4.90</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>80,065</t>
+          <t>125,264</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>115/06/01</t>
+          <t>115/05/04</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>135817122</t>
+          <t>125270935</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>14,329,024,058</t>
+          <t>11,748,311,547</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>105.25</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>106.70</t>
+          <t>94.65</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>104.50</t>
+          <t>92.40</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>105.50</t>
+          <t>94.60</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>+0.10</t>
+          <t>+4.10</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>156,361</t>
+          <t>114,510</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>115/06/02</t>
+          <t>115/05/05</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>117160979</t>
+          <t>82851869</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>12,341,210,929</t>
+          <t>7,821,971,023</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>106.30</t>
+          <t>94.40</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>106.30</t>
+          <t>94.75</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>104.20</t>
+          <t>94.00</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>105.70</t>
+          <t>94.60</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>+0.20</t>
+          <t xml:space="preserve"> 0.00</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>164,814</t>
+          <t>115,951</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>115/06/03</t>
+          <t>115/05/06</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>79592362</t>
+          <t>111759164</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>8,559,208,311</t>
+          <t>10,703,702,958</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>107.30</t>
+          <t>96.05</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>107.85</t>
+          <t>96.90</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>107.10</t>
+          <t>94.70</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>107.60</t>
+          <t>95.75</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>+1.90</t>
+          <t>+1.15</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>86,991</t>
+          <t>120,555</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>115/06/04</t>
+          <t>115/05/07</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>236782252</t>
+          <t>117152238</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>25,181,889,523</t>
+          <t>11,472,448,704</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>106.75</t>
+          <t>97.95</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>107.00</t>
+          <t>98.40</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>106.05</t>
+          <t>97.40</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>106.10</t>
+          <t>97.70</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>+1.95</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>210,220</t>
+          <t>119,685</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
+          <t>115/05/08</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>131188123</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>12,716,275,565</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>97.35</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>97.70</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>95.85</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>97.00</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-0.70</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>217,822</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>115/05/11</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>96606391</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>9,362,479,353</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>96.65</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>97.15</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>96.50</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>96.90</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>148,902</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>115/05/12</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>102303450</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>9,876,959,425</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>96.85</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>97.35</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>95.50</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>96.85</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>142,949</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>115/05/13</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>130654061</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>12,419,149,243</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>94.85</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>95.80</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>94.70</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>95.50</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>260,692</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>115/05/14</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>57229209</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>5,510,647,058</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>96.90</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>97.20</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>95.75</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>96.05</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>+0.55</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>70,419</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>115/05/15</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>98132989</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>9,472,541,597</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>97.65</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>98.25</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>95.20</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>95.40</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>144,425</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>115/05/18</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>118571453</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>11,160,721,206</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>94.00</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>95.20</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>93.30</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>94.90</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>219,202</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>115/05/19</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>135939820</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>12,740,872,880</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>94.35</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>94.70</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>93.10</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>93.10</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-1.80</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>304,750</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>115/05/20</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>121650308</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>11,289,688,382</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>93.00</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>93.50</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>92.45</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>92.50</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>227,369</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>115/05/21</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>62215954</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>5,942,503,747</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>94.80</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>96.05</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>94.70</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>95.85</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>+3.35</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>64,187</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>115/05/22</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>64288280</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>6,213,742,970</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>96.30</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>97.30</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>96.00</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>97.30</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>+1.45</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>70,101</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>115/05/25</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>129483256</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>13,010,032,076</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>99.55</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>99.55</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>100.80</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>+3.50</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>107,787</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>115/05/26</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>93560313</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>9,432,115,613</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>101.60</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>101.80</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>100.10</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>100.10</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-0.70</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>112,958</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>115/05/27</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>94959812</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>9,787,482,181</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>102.40</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>103.90</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>102.00</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>102.55</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>+2.45</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>98,413</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>115/05/28</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>152915695</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>15,600,509,184</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>104.00</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>104.25</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>100.10</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>100.50</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>207,536</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>115/05/29</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>102355526</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>10,636,250,508</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>103.20</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>105.40</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>102.70</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>105.40</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>+4.90</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>80,065</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>115/06/01</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>135817122</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>14,329,024,058</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>105.25</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>106.70</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>104.50</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>105.50</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>+0.10</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>156,361</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>115/06/02</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>117160979</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>12,341,210,929</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>106.30</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>106.30</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>104.20</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>105.70</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>+0.20</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>164,814</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>115/06/03</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>79592362</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>8,559,208,311</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>107.30</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>107.85</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>107.10</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>107.60</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>+1.90</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>86,991</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>115/06/04</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>236782252</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>25,181,889,523</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>106.75</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>107.00</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>106.05</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>106.10</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-1.50</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>210,220</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
           <t>115/06/05</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>337031371</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C228" t="inlineStr">
         <is>
           <t>34,914,259,576</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>105.00</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E228" t="inlineStr">
         <is>
           <t>105.35</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="F228" t="inlineStr">
         <is>
           <t>102.80</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G228" t="inlineStr">
         <is>
           <t>104.15</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
+      <c r="H228" t="inlineStr">
         <is>
           <t>-1.95</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
+      <c r="I228" t="inlineStr">
         <is>
           <t>355,384</t>
         </is>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I228"/>
+  <dimension ref="A1:I229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11144,6 +11144,53 @@
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>115/06/08</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>524952235</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>52,211,365,308</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>98.05</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>101.30</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>98.05</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>100.95</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-3.20</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>599,172</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I229"/>
+  <dimension ref="A1:I230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11191,6 +11191,53 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>115/06/09</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>246039378</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>25,054,932,573</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>102.10</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>103.60</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>101.35</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>103.50</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>+2.55</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>121,189</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/0050_one year.xlsx
+++ b/0050_one year.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I230"/>
+  <dimension ref="A1:I231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11238,6 +11238,53 @@
         </is>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>115/06/10</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>192916596</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>19,540,045,300</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>102.60</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>102.95</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>100.20</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>100.25</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-3.25</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>423,917</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
